--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -1,37 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>Código Produto</t>
+  </si>
+  <si>
+    <t>Descrição Produto</t>
+  </si>
+  <si>
+    <t>Qtde Atendida</t>
+  </si>
+  <si>
+    <t>Operação</t>
+  </si>
+  <si>
+    <t>Processo</t>
+  </si>
+  <si>
+    <t>Status Processo</t>
+  </si>
+  <si>
+    <t>Data Aceite</t>
+  </si>
+  <si>
+    <t>Valor Orçado</t>
+  </si>
+  <si>
+    <t>Valor Realizado</t>
+  </si>
+  <si>
+    <t>Consultor Interno</t>
+  </si>
+  <si>
+    <t>Representante-pedido</t>
+  </si>
+  <si>
+    <t>Gerente Comercial-Pedido</t>
+  </si>
+  <si>
+    <t>Aplicação Mat./Serv.</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Nome Cliente</t>
+  </si>
+  <si>
+    <t>Cidade</t>
+  </si>
+  <si>
+    <t>UF</t>
+  </si>
+  <si>
+    <t>Tipo de Mercadoria</t>
+  </si>
+  <si>
+    <t>Subgrupo</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Negócio</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +117,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,122 +433,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:U1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Código Produto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Descrição Produto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Qtde Atendida</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Operação</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Processo</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Status Processo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Data Aceite</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Orçado</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Realizado</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Consultor Interno</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Representante-pedido</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Gerente Comercial-Pedido</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Aplicação Mat./Serv.</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Nome Cliente</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Cidade</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>UF</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de Mercadoria</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Subgrupo</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Negócio</t>
-        </is>
+    <row r="1" spans="1:21">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="341">
   <si>
     <t>Código Produto</t>
   </si>
@@ -37,9 +37,6 @@
     <t>Data Aceite</t>
   </si>
   <si>
-    <t>Valor Orçado</t>
-  </si>
-  <si>
     <t>Valor Realizado</t>
   </si>
   <si>
@@ -77,12 +74,978 @@
   </si>
   <si>
     <t>Negócio</t>
+  </si>
+  <si>
+    <t>PROD100003</t>
+  </si>
+  <si>
+    <t>PROD100004</t>
+  </si>
+  <si>
+    <t>PROD100006</t>
+  </si>
+  <si>
+    <t>PROD100007</t>
+  </si>
+  <si>
+    <t>PROD100009</t>
+  </si>
+  <si>
+    <t>PROD100010</t>
+  </si>
+  <si>
+    <t>PROD200001</t>
+  </si>
+  <si>
+    <t>PROD200002</t>
+  </si>
+  <si>
+    <t>PROD200003</t>
+  </si>
+  <si>
+    <t>PROD200004</t>
+  </si>
+  <si>
+    <t>PROD200005</t>
+  </si>
+  <si>
+    <t>PROD200006</t>
+  </si>
+  <si>
+    <t>PROD200007</t>
+  </si>
+  <si>
+    <t>PROD200008</t>
+  </si>
+  <si>
+    <t>PROD200009</t>
+  </si>
+  <si>
+    <t>PROD2000010</t>
+  </si>
+  <si>
+    <t>PROD2000011</t>
+  </si>
+  <si>
+    <t>PROD2000012</t>
+  </si>
+  <si>
+    <t>PROD200013</t>
+  </si>
+  <si>
+    <t>PROD200014</t>
+  </si>
+  <si>
+    <t>PROD200015</t>
+  </si>
+  <si>
+    <t>PROD200016</t>
+  </si>
+  <si>
+    <t>PROD200017</t>
+  </si>
+  <si>
+    <t>PROD200018</t>
+  </si>
+  <si>
+    <t>PROD200019</t>
+  </si>
+  <si>
+    <t>PROD200025</t>
+  </si>
+  <si>
+    <t>PROD200026</t>
+  </si>
+  <si>
+    <t>PROD200028</t>
+  </si>
+  <si>
+    <t>PROD200029</t>
+  </si>
+  <si>
+    <t>PROD200031</t>
+  </si>
+  <si>
+    <t>PROD200032</t>
+  </si>
+  <si>
+    <t>PROD200033</t>
+  </si>
+  <si>
+    <t>PROD200034</t>
+  </si>
+  <si>
+    <t>PROD200035</t>
+  </si>
+  <si>
+    <t>PROD200036</t>
+  </si>
+  <si>
+    <t>PROD200037</t>
+  </si>
+  <si>
+    <t>PROD200038</t>
+  </si>
+  <si>
+    <t>PROD200039</t>
+  </si>
+  <si>
+    <t>PROD200046</t>
+  </si>
+  <si>
+    <t>PROD200047</t>
+  </si>
+  <si>
+    <t>PROD200049</t>
+  </si>
+  <si>
+    <t>PROD200050</t>
+  </si>
+  <si>
+    <t>PROD300009</t>
+  </si>
+  <si>
+    <t>PROD300010</t>
+  </si>
+  <si>
+    <t>PROD300031</t>
+  </si>
+  <si>
+    <t>PROD300032</t>
+  </si>
+  <si>
+    <t>PROD300033</t>
+  </si>
+  <si>
+    <t>PROD300034</t>
+  </si>
+  <si>
+    <t>PROD300035</t>
+  </si>
+  <si>
+    <t>PROD300036</t>
+  </si>
+  <si>
+    <t>PROD300037</t>
+  </si>
+  <si>
+    <t>PROD300038</t>
+  </si>
+  <si>
+    <t>PROD300039</t>
+  </si>
+  <si>
+    <t>PROD300040</t>
+  </si>
+  <si>
+    <t>PROD300041</t>
+  </si>
+  <si>
+    <t>PROD300042</t>
+  </si>
+  <si>
+    <t>PROD300043</t>
+  </si>
+  <si>
+    <t>PROD300044</t>
+  </si>
+  <si>
+    <t>PROD300045</t>
+  </si>
+  <si>
+    <t>PROD300046</t>
+  </si>
+  <si>
+    <t>PROD300047</t>
+  </si>
+  <si>
+    <t>PROD300048</t>
+  </si>
+  <si>
+    <t>PROD300049</t>
+  </si>
+  <si>
+    <t>PROD400004</t>
+  </si>
+  <si>
+    <t>PROD400005</t>
+  </si>
+  <si>
+    <t>PROD400006</t>
+  </si>
+  <si>
+    <t>PROD400009</t>
+  </si>
+  <si>
+    <t>PROD4000010</t>
+  </si>
+  <si>
+    <t>PROD500007</t>
+  </si>
+  <si>
+    <t>PROD500008</t>
+  </si>
+  <si>
+    <t>PROD500010</t>
+  </si>
+  <si>
+    <t>PROD500011</t>
+  </si>
+  <si>
+    <t>PROD500012</t>
+  </si>
+  <si>
+    <t>PROD500013</t>
+  </si>
+  <si>
+    <t>PROD500014</t>
+  </si>
+  <si>
+    <t>PROD500015</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100003</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100004</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100006</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100007</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100009</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100010</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200001</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200002</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200003</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200004</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200005</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200006</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200007</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200008</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200009</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 2000010</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 2000011</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 2000012</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200013</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200014</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200015</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200016</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200017</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200018</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200019</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200025</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200026</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200028</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200029</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200031</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200032</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200033</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200034</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200035</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200036</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200037</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200038</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200039</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200046</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200047</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200049</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 200050</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300009</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300010</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300031</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300032</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300033</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300034</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300035</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300036</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300037</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300038</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300039</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300040</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300041</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300042</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300043</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300044</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300045</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300046</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300047</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300048</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 300049</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400004</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400005</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400006</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400009</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 4000010</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500007</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500008</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500010</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500011</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500012</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500013</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500014</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 500015</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PVEN - Produto Venda</t>
+  </si>
+  <si>
+    <t>100003</t>
+  </si>
+  <si>
+    <t>100004</t>
+  </si>
+  <si>
+    <t>100006</t>
+  </si>
+  <si>
+    <t>100007</t>
+  </si>
+  <si>
+    <t>100009</t>
+  </si>
+  <si>
+    <t>100010</t>
+  </si>
+  <si>
+    <t>200001</t>
+  </si>
+  <si>
+    <t>200002</t>
+  </si>
+  <si>
+    <t>200003</t>
+  </si>
+  <si>
+    <t>200004</t>
+  </si>
+  <si>
+    <t>200005</t>
+  </si>
+  <si>
+    <t>200006</t>
+  </si>
+  <si>
+    <t>200007</t>
+  </si>
+  <si>
+    <t>200008</t>
+  </si>
+  <si>
+    <t>200009</t>
+  </si>
+  <si>
+    <t>2000010</t>
+  </si>
+  <si>
+    <t>2000011</t>
+  </si>
+  <si>
+    <t>2000012</t>
+  </si>
+  <si>
+    <t>200013</t>
+  </si>
+  <si>
+    <t>200014</t>
+  </si>
+  <si>
+    <t>200015</t>
+  </si>
+  <si>
+    <t>200016</t>
+  </si>
+  <si>
+    <t>200017</t>
+  </si>
+  <si>
+    <t>200018</t>
+  </si>
+  <si>
+    <t>200019</t>
+  </si>
+  <si>
+    <t>200025</t>
+  </si>
+  <si>
+    <t>200026</t>
+  </si>
+  <si>
+    <t>200028</t>
+  </si>
+  <si>
+    <t>200029</t>
+  </si>
+  <si>
+    <t>200031</t>
+  </si>
+  <si>
+    <t>200032</t>
+  </si>
+  <si>
+    <t>200033</t>
+  </si>
+  <si>
+    <t>200034</t>
+  </si>
+  <si>
+    <t>200035</t>
+  </si>
+  <si>
+    <t>200036</t>
+  </si>
+  <si>
+    <t>200037</t>
+  </si>
+  <si>
+    <t>200038</t>
+  </si>
+  <si>
+    <t>200039</t>
+  </si>
+  <si>
+    <t>200046</t>
+  </si>
+  <si>
+    <t>200047</t>
+  </si>
+  <si>
+    <t>200049</t>
+  </si>
+  <si>
+    <t>200050</t>
+  </si>
+  <si>
+    <t>300009</t>
+  </si>
+  <si>
+    <t>300010</t>
+  </si>
+  <si>
+    <t>300031</t>
+  </si>
+  <si>
+    <t>300032</t>
+  </si>
+  <si>
+    <t>300033</t>
+  </si>
+  <si>
+    <t>300034</t>
+  </si>
+  <si>
+    <t>300035</t>
+  </si>
+  <si>
+    <t>300036</t>
+  </si>
+  <si>
+    <t>300037</t>
+  </si>
+  <si>
+    <t>300038</t>
+  </si>
+  <si>
+    <t>300039</t>
+  </si>
+  <si>
+    <t>300040</t>
+  </si>
+  <si>
+    <t>300041</t>
+  </si>
+  <si>
+    <t>300042</t>
+  </si>
+  <si>
+    <t>300043</t>
+  </si>
+  <si>
+    <t>300044</t>
+  </si>
+  <si>
+    <t>300045</t>
+  </si>
+  <si>
+    <t>300046</t>
+  </si>
+  <si>
+    <t>300047</t>
+  </si>
+  <si>
+    <t>300048</t>
+  </si>
+  <si>
+    <t>300049</t>
+  </si>
+  <si>
+    <t>400004</t>
+  </si>
+  <si>
+    <t>400005</t>
+  </si>
+  <si>
+    <t>400006</t>
+  </si>
+  <si>
+    <t>400009</t>
+  </si>
+  <si>
+    <t>4000010</t>
+  </si>
+  <si>
+    <t>500007</t>
+  </si>
+  <si>
+    <t>500008</t>
+  </si>
+  <si>
+    <t>500010</t>
+  </si>
+  <si>
+    <t>500011</t>
+  </si>
+  <si>
+    <t>500012</t>
+  </si>
+  <si>
+    <t>500013</t>
+  </si>
+  <si>
+    <t>500014</t>
+  </si>
+  <si>
+    <t>500015</t>
+  </si>
+  <si>
+    <t>FATURADO</t>
+  </si>
+  <si>
+    <t>PENDENTE</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>13300</t>
+  </si>
+  <si>
+    <t>13400</t>
+  </si>
+  <si>
+    <t>13500</t>
+  </si>
+  <si>
+    <t>13600</t>
+  </si>
+  <si>
+    <t>13700</t>
+  </si>
+  <si>
+    <t>13800</t>
+  </si>
+  <si>
+    <t>13900</t>
+  </si>
+  <si>
+    <t>14500</t>
+  </si>
+  <si>
+    <t>14600</t>
+  </si>
+  <si>
+    <t>14800</t>
+  </si>
+  <si>
+    <t>14900</t>
+  </si>
+  <si>
+    <t>15100</t>
+  </si>
+  <si>
+    <t>15200</t>
+  </si>
+  <si>
+    <t>15300</t>
+  </si>
+  <si>
+    <t>15400</t>
+  </si>
+  <si>
+    <t>15500</t>
+  </si>
+  <si>
+    <t>15600</t>
+  </si>
+  <si>
+    <t>15700</t>
+  </si>
+  <si>
+    <t>15800</t>
+  </si>
+  <si>
+    <t>15900</t>
+  </si>
+  <si>
+    <t>16600</t>
+  </si>
+  <si>
+    <t>16700</t>
+  </si>
+  <si>
+    <t>16900</t>
+  </si>
+  <si>
+    <t>17000</t>
+  </si>
+  <si>
+    <t>28000</t>
+  </si>
+  <si>
+    <t>32000</t>
+  </si>
+  <si>
+    <t>25500</t>
+  </si>
+  <si>
+    <t>26000</t>
+  </si>
+  <si>
+    <t>26500</t>
+  </si>
+  <si>
+    <t>27000</t>
+  </si>
+  <si>
+    <t>27500</t>
+  </si>
+  <si>
+    <t>28500</t>
+  </si>
+  <si>
+    <t>29000</t>
+  </si>
+  <si>
+    <t>29500</t>
+  </si>
+  <si>
+    <t>30500</t>
+  </si>
+  <si>
+    <t>31000</t>
+  </si>
+  <si>
+    <t>31500</t>
+  </si>
+  <si>
+    <t>32500</t>
+  </si>
+  <si>
+    <t>33000</t>
+  </si>
+  <si>
+    <t>33500</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>34500</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
+    <t>55000</t>
+  </si>
+  <si>
+    <t>38000</t>
+  </si>
+  <si>
+    <t>42000</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>37500</t>
+  </si>
+  <si>
+    <t>Alessandro Cappi</t>
+  </si>
+  <si>
+    <t>André Caramello</t>
+  </si>
+  <si>
+    <t>Mateus Machado</t>
+  </si>
+  <si>
+    <t>Andrey Andrade</t>
+  </si>
+  <si>
+    <t>André Camargo</t>
+  </si>
+  <si>
+    <t>Industrial</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>CLIENTE TESTE LTDA</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>Serviço</t>
+  </si>
+  <si>
+    <t>Aluguel</t>
+  </si>
+  <si>
+    <t>Reposição</t>
+  </si>
+  <si>
+    <t>Falco</t>
+  </si>
+  <si>
+    <t>Acessório</t>
+  </si>
+  <si>
+    <t>Calibração</t>
+  </si>
+  <si>
+    <t>ISCO</t>
+  </si>
+  <si>
+    <t>Innova</t>
+  </si>
+  <si>
+    <t>QED</t>
+  </si>
+  <si>
+    <t>YSI</t>
+  </si>
+  <si>
+    <t>Thermo</t>
+  </si>
+  <si>
+    <t>MicroClip</t>
+  </si>
+  <si>
+    <t>Analisador Fixo</t>
+  </si>
+  <si>
+    <t>Analisador Portátil</t>
+  </si>
+  <si>
+    <t>Diversos Diversos</t>
+  </si>
+  <si>
+    <t>Equipamento Amostragem</t>
+  </si>
+  <si>
+    <t>Sistema Remediação</t>
+  </si>
+  <si>
+    <t>Detector Portátil</t>
+  </si>
+  <si>
+    <t>SSO</t>
+  </si>
+  <si>
+    <t>Hidrologia</t>
+  </si>
+  <si>
+    <t>Remediação</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -135,11 +1098,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,10 +1398,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:T86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -498,8 +1462,4798 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" t="s">
         <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45870</v>
+      </c>
+      <c r="H2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I2" t="s">
+        <v>309</v>
+      </c>
+      <c r="L2" t="s">
+        <v>314</v>
+      </c>
+      <c r="M2" t="s">
+        <v>315</v>
+      </c>
+      <c r="N2" t="s">
+        <v>316</v>
+      </c>
+      <c r="O2" t="s">
+        <v>317</v>
+      </c>
+      <c r="P2" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>319</v>
+      </c>
+      <c r="R2" t="s">
+        <v>323</v>
+      </c>
+      <c r="S2" t="s">
+        <v>332</v>
+      </c>
+      <c r="T2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G3" s="2">
+        <v>45875</v>
+      </c>
+      <c r="H3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I3" t="s">
+        <v>309</v>
+      </c>
+      <c r="L3" t="s">
+        <v>314</v>
+      </c>
+      <c r="M3" t="s">
+        <v>315</v>
+      </c>
+      <c r="N3" t="s">
+        <v>316</v>
+      </c>
+      <c r="O3" t="s">
+        <v>317</v>
+      </c>
+      <c r="P3" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>319</v>
+      </c>
+      <c r="R3" t="s">
+        <v>323</v>
+      </c>
+      <c r="S3" t="s">
+        <v>332</v>
+      </c>
+      <c r="T3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" t="s">
+        <v>250</v>
+      </c>
+      <c r="G4" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H4" t="s">
+        <v>254</v>
+      </c>
+      <c r="I4" t="s">
+        <v>309</v>
+      </c>
+      <c r="L4" t="s">
+        <v>314</v>
+      </c>
+      <c r="M4" t="s">
+        <v>315</v>
+      </c>
+      <c r="N4" t="s">
+        <v>316</v>
+      </c>
+      <c r="O4" t="s">
+        <v>317</v>
+      </c>
+      <c r="P4" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>319</v>
+      </c>
+      <c r="R4" t="s">
+        <v>323</v>
+      </c>
+      <c r="S4" t="s">
+        <v>332</v>
+      </c>
+      <c r="T4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" t="s">
+        <v>250</v>
+      </c>
+      <c r="G5" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H5" t="s">
+        <v>255</v>
+      </c>
+      <c r="I5" t="s">
+        <v>310</v>
+      </c>
+      <c r="L5" t="s">
+        <v>314</v>
+      </c>
+      <c r="M5" t="s">
+        <v>315</v>
+      </c>
+      <c r="N5" t="s">
+        <v>316</v>
+      </c>
+      <c r="O5" t="s">
+        <v>317</v>
+      </c>
+      <c r="P5" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>319</v>
+      </c>
+      <c r="R5" t="s">
+        <v>324</v>
+      </c>
+      <c r="S5" t="s">
+        <v>333</v>
+      </c>
+      <c r="T5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" t="s">
+        <v>250</v>
+      </c>
+      <c r="G6" s="2">
+        <v>45885</v>
+      </c>
+      <c r="H6" t="s">
+        <v>256</v>
+      </c>
+      <c r="I6" t="s">
+        <v>309</v>
+      </c>
+      <c r="L6" t="s">
+        <v>314</v>
+      </c>
+      <c r="M6" t="s">
+        <v>315</v>
+      </c>
+      <c r="N6" t="s">
+        <v>316</v>
+      </c>
+      <c r="O6" t="s">
+        <v>317</v>
+      </c>
+      <c r="P6" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>320</v>
+      </c>
+      <c r="R6" t="s">
+        <v>325</v>
+      </c>
+      <c r="S6" t="s">
+        <v>334</v>
+      </c>
+      <c r="T6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45872</v>
+      </c>
+      <c r="H7" t="s">
+        <v>257</v>
+      </c>
+      <c r="I7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L7" t="s">
+        <v>314</v>
+      </c>
+      <c r="M7" t="s">
+        <v>315</v>
+      </c>
+      <c r="N7" t="s">
+        <v>316</v>
+      </c>
+      <c r="O7" t="s">
+        <v>317</v>
+      </c>
+      <c r="P7" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>319</v>
+      </c>
+      <c r="R7" t="s">
+        <v>323</v>
+      </c>
+      <c r="S7" t="s">
+        <v>332</v>
+      </c>
+      <c r="T7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" t="s">
+        <v>250</v>
+      </c>
+      <c r="G8" s="2">
+        <v>45888</v>
+      </c>
+      <c r="H8" t="s">
+        <v>252</v>
+      </c>
+      <c r="I8" t="s">
+        <v>309</v>
+      </c>
+      <c r="L8" t="s">
+        <v>314</v>
+      </c>
+      <c r="M8" t="s">
+        <v>315</v>
+      </c>
+      <c r="N8" t="s">
+        <v>316</v>
+      </c>
+      <c r="O8" t="s">
+        <v>317</v>
+      </c>
+      <c r="P8" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>319</v>
+      </c>
+      <c r="R8" t="s">
+        <v>323</v>
+      </c>
+      <c r="S8" t="s">
+        <v>332</v>
+      </c>
+      <c r="T8" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F9" t="s">
+        <v>250</v>
+      </c>
+      <c r="G9" s="2">
+        <v>45871</v>
+      </c>
+      <c r="H9" t="s">
+        <v>258</v>
+      </c>
+      <c r="I9" t="s">
+        <v>309</v>
+      </c>
+      <c r="L9" t="s">
+        <v>314</v>
+      </c>
+      <c r="M9" t="s">
+        <v>315</v>
+      </c>
+      <c r="N9" t="s">
+        <v>316</v>
+      </c>
+      <c r="O9" t="s">
+        <v>317</v>
+      </c>
+      <c r="P9" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>319</v>
+      </c>
+      <c r="R9" t="s">
+        <v>323</v>
+      </c>
+      <c r="S9" t="s">
+        <v>332</v>
+      </c>
+      <c r="T9" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F10" t="s">
+        <v>250</v>
+      </c>
+      <c r="G10" s="2">
+        <v>45872</v>
+      </c>
+      <c r="H10" t="s">
+        <v>258</v>
+      </c>
+      <c r="I10" t="s">
+        <v>309</v>
+      </c>
+      <c r="L10" t="s">
+        <v>314</v>
+      </c>
+      <c r="M10" t="s">
+        <v>315</v>
+      </c>
+      <c r="N10" t="s">
+        <v>316</v>
+      </c>
+      <c r="O10" t="s">
+        <v>317</v>
+      </c>
+      <c r="P10" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>319</v>
+      </c>
+      <c r="R10" t="s">
+        <v>323</v>
+      </c>
+      <c r="S10" t="s">
+        <v>332</v>
+      </c>
+      <c r="T10" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" t="s">
+        <v>172</v>
+      </c>
+      <c r="D11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F11" t="s">
+        <v>250</v>
+      </c>
+      <c r="G11" s="2">
+        <v>45873</v>
+      </c>
+      <c r="H11" t="s">
+        <v>258</v>
+      </c>
+      <c r="I11" t="s">
+        <v>309</v>
+      </c>
+      <c r="L11" t="s">
+        <v>314</v>
+      </c>
+      <c r="M11" t="s">
+        <v>315</v>
+      </c>
+      <c r="N11" t="s">
+        <v>316</v>
+      </c>
+      <c r="O11" t="s">
+        <v>317</v>
+      </c>
+      <c r="P11" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>319</v>
+      </c>
+      <c r="R11" t="s">
+        <v>323</v>
+      </c>
+      <c r="S11" t="s">
+        <v>332</v>
+      </c>
+      <c r="T11" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" t="s">
+        <v>183</v>
+      </c>
+      <c r="F12" t="s">
+        <v>250</v>
+      </c>
+      <c r="G12" s="2">
+        <v>45874</v>
+      </c>
+      <c r="H12" t="s">
+        <v>258</v>
+      </c>
+      <c r="I12" t="s">
+        <v>309</v>
+      </c>
+      <c r="L12" t="s">
+        <v>314</v>
+      </c>
+      <c r="M12" t="s">
+        <v>315</v>
+      </c>
+      <c r="N12" t="s">
+        <v>316</v>
+      </c>
+      <c r="O12" t="s">
+        <v>317</v>
+      </c>
+      <c r="P12" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>319</v>
+      </c>
+      <c r="R12" t="s">
+        <v>323</v>
+      </c>
+      <c r="S12" t="s">
+        <v>332</v>
+      </c>
+      <c r="T12" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E13" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" t="s">
+        <v>250</v>
+      </c>
+      <c r="G13" s="2">
+        <v>45875</v>
+      </c>
+      <c r="H13" t="s">
+        <v>258</v>
+      </c>
+      <c r="I13" t="s">
+        <v>309</v>
+      </c>
+      <c r="L13" t="s">
+        <v>314</v>
+      </c>
+      <c r="M13" t="s">
+        <v>315</v>
+      </c>
+      <c r="N13" t="s">
+        <v>316</v>
+      </c>
+      <c r="O13" t="s">
+        <v>317</v>
+      </c>
+      <c r="P13" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>319</v>
+      </c>
+      <c r="R13" t="s">
+        <v>323</v>
+      </c>
+      <c r="S13" t="s">
+        <v>332</v>
+      </c>
+      <c r="T13" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" t="s">
+        <v>250</v>
+      </c>
+      <c r="G14" s="2">
+        <v>45876</v>
+      </c>
+      <c r="H14" t="s">
+        <v>258</v>
+      </c>
+      <c r="I14" t="s">
+        <v>309</v>
+      </c>
+      <c r="L14" t="s">
+        <v>314</v>
+      </c>
+      <c r="M14" t="s">
+        <v>315</v>
+      </c>
+      <c r="N14" t="s">
+        <v>316</v>
+      </c>
+      <c r="O14" t="s">
+        <v>317</v>
+      </c>
+      <c r="P14" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>319</v>
+      </c>
+      <c r="R14" t="s">
+        <v>323</v>
+      </c>
+      <c r="S14" t="s">
+        <v>332</v>
+      </c>
+      <c r="T14" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D15" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F15" t="s">
+        <v>250</v>
+      </c>
+      <c r="G15" s="2">
+        <v>45872</v>
+      </c>
+      <c r="H15" t="s">
+        <v>252</v>
+      </c>
+      <c r="I15" t="s">
+        <v>309</v>
+      </c>
+      <c r="L15" t="s">
+        <v>314</v>
+      </c>
+      <c r="M15" t="s">
+        <v>315</v>
+      </c>
+      <c r="N15" t="s">
+        <v>316</v>
+      </c>
+      <c r="O15" t="s">
+        <v>317</v>
+      </c>
+      <c r="P15" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>319</v>
+      </c>
+      <c r="R15" t="s">
+        <v>326</v>
+      </c>
+      <c r="S15" t="s">
+        <v>335</v>
+      </c>
+      <c r="T15" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F16" t="s">
+        <v>250</v>
+      </c>
+      <c r="G16" s="2">
+        <v>45873</v>
+      </c>
+      <c r="H16" t="s">
+        <v>252</v>
+      </c>
+      <c r="I16" t="s">
+        <v>309</v>
+      </c>
+      <c r="L16" t="s">
+        <v>314</v>
+      </c>
+      <c r="M16" t="s">
+        <v>315</v>
+      </c>
+      <c r="N16" t="s">
+        <v>316</v>
+      </c>
+      <c r="O16" t="s">
+        <v>317</v>
+      </c>
+      <c r="P16" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>319</v>
+      </c>
+      <c r="R16" t="s">
+        <v>326</v>
+      </c>
+      <c r="S16" t="s">
+        <v>335</v>
+      </c>
+      <c r="T16" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" t="s">
+        <v>173</v>
+      </c>
+      <c r="E17" t="s">
+        <v>188</v>
+      </c>
+      <c r="F17" t="s">
+        <v>250</v>
+      </c>
+      <c r="G17" s="2">
+        <v>45874</v>
+      </c>
+      <c r="H17" t="s">
+        <v>252</v>
+      </c>
+      <c r="I17" t="s">
+        <v>309</v>
+      </c>
+      <c r="L17" t="s">
+        <v>314</v>
+      </c>
+      <c r="M17" t="s">
+        <v>315</v>
+      </c>
+      <c r="N17" t="s">
+        <v>316</v>
+      </c>
+      <c r="O17" t="s">
+        <v>317</v>
+      </c>
+      <c r="P17" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>319</v>
+      </c>
+      <c r="R17" t="s">
+        <v>326</v>
+      </c>
+      <c r="S17" t="s">
+        <v>335</v>
+      </c>
+      <c r="T17" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" t="s">
+        <v>250</v>
+      </c>
+      <c r="G18" s="2">
+        <v>45875</v>
+      </c>
+      <c r="H18" t="s">
+        <v>252</v>
+      </c>
+      <c r="I18" t="s">
+        <v>309</v>
+      </c>
+      <c r="L18" t="s">
+        <v>314</v>
+      </c>
+      <c r="M18" t="s">
+        <v>315</v>
+      </c>
+      <c r="N18" t="s">
+        <v>316</v>
+      </c>
+      <c r="O18" t="s">
+        <v>317</v>
+      </c>
+      <c r="P18" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>319</v>
+      </c>
+      <c r="R18" t="s">
+        <v>326</v>
+      </c>
+      <c r="S18" t="s">
+        <v>335</v>
+      </c>
+      <c r="T18" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" t="s">
+        <v>173</v>
+      </c>
+      <c r="E19" t="s">
+        <v>190</v>
+      </c>
+      <c r="F19" t="s">
+        <v>250</v>
+      </c>
+      <c r="G19" s="2">
+        <v>45876</v>
+      </c>
+      <c r="H19" t="s">
+        <v>252</v>
+      </c>
+      <c r="I19" t="s">
+        <v>309</v>
+      </c>
+      <c r="L19" t="s">
+        <v>314</v>
+      </c>
+      <c r="M19" t="s">
+        <v>315</v>
+      </c>
+      <c r="N19" t="s">
+        <v>316</v>
+      </c>
+      <c r="O19" t="s">
+        <v>317</v>
+      </c>
+      <c r="P19" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>319</v>
+      </c>
+      <c r="R19" t="s">
+        <v>326</v>
+      </c>
+      <c r="S19" t="s">
+        <v>335</v>
+      </c>
+      <c r="T19" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" t="s">
+        <v>173</v>
+      </c>
+      <c r="E20" t="s">
+        <v>191</v>
+      </c>
+      <c r="F20" t="s">
+        <v>250</v>
+      </c>
+      <c r="G20" s="2">
+        <v>45877</v>
+      </c>
+      <c r="H20" t="s">
+        <v>252</v>
+      </c>
+      <c r="I20" t="s">
+        <v>309</v>
+      </c>
+      <c r="L20" t="s">
+        <v>314</v>
+      </c>
+      <c r="M20" t="s">
+        <v>315</v>
+      </c>
+      <c r="N20" t="s">
+        <v>316</v>
+      </c>
+      <c r="O20" t="s">
+        <v>317</v>
+      </c>
+      <c r="P20" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>319</v>
+      </c>
+      <c r="R20" t="s">
+        <v>326</v>
+      </c>
+      <c r="S20" t="s">
+        <v>335</v>
+      </c>
+      <c r="T20" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F21" t="s">
+        <v>250</v>
+      </c>
+      <c r="G21" s="2">
+        <v>45878</v>
+      </c>
+      <c r="H21" t="s">
+        <v>259</v>
+      </c>
+      <c r="I21" t="s">
+        <v>309</v>
+      </c>
+      <c r="L21" t="s">
+        <v>314</v>
+      </c>
+      <c r="M21" t="s">
+        <v>315</v>
+      </c>
+      <c r="N21" t="s">
+        <v>316</v>
+      </c>
+      <c r="O21" t="s">
+        <v>317</v>
+      </c>
+      <c r="P21" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>319</v>
+      </c>
+      <c r="R21" t="s">
+        <v>323</v>
+      </c>
+      <c r="S21" t="s">
+        <v>332</v>
+      </c>
+      <c r="T21" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" t="s">
+        <v>193</v>
+      </c>
+      <c r="F22" t="s">
+        <v>250</v>
+      </c>
+      <c r="G22" s="2">
+        <v>45879</v>
+      </c>
+      <c r="H22" t="s">
+        <v>260</v>
+      </c>
+      <c r="I22" t="s">
+        <v>309</v>
+      </c>
+      <c r="L22" t="s">
+        <v>314</v>
+      </c>
+      <c r="M22" t="s">
+        <v>315</v>
+      </c>
+      <c r="N22" t="s">
+        <v>316</v>
+      </c>
+      <c r="O22" t="s">
+        <v>317</v>
+      </c>
+      <c r="P22" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>319</v>
+      </c>
+      <c r="R22" t="s">
+        <v>323</v>
+      </c>
+      <c r="S22" t="s">
+        <v>332</v>
+      </c>
+      <c r="T22" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" t="s">
+        <v>172</v>
+      </c>
+      <c r="D23" t="s">
+        <v>173</v>
+      </c>
+      <c r="E23" t="s">
+        <v>194</v>
+      </c>
+      <c r="F23" t="s">
+        <v>251</v>
+      </c>
+      <c r="G23" s="2">
+        <v>45874</v>
+      </c>
+      <c r="H23" t="s">
+        <v>261</v>
+      </c>
+      <c r="I23" t="s">
+        <v>309</v>
+      </c>
+      <c r="L23" t="s">
+        <v>314</v>
+      </c>
+      <c r="M23" t="s">
+        <v>315</v>
+      </c>
+      <c r="N23" t="s">
+        <v>316</v>
+      </c>
+      <c r="O23" t="s">
+        <v>317</v>
+      </c>
+      <c r="P23" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>319</v>
+      </c>
+      <c r="R23" t="s">
+        <v>323</v>
+      </c>
+      <c r="S23" t="s">
+        <v>332</v>
+      </c>
+      <c r="T23" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" t="s">
+        <v>195</v>
+      </c>
+      <c r="F24" t="s">
+        <v>250</v>
+      </c>
+      <c r="G24" s="2">
+        <v>45881</v>
+      </c>
+      <c r="H24" t="s">
+        <v>262</v>
+      </c>
+      <c r="I24" t="s">
+        <v>309</v>
+      </c>
+      <c r="L24" t="s">
+        <v>314</v>
+      </c>
+      <c r="M24" t="s">
+        <v>315</v>
+      </c>
+      <c r="N24" t="s">
+        <v>316</v>
+      </c>
+      <c r="O24" t="s">
+        <v>317</v>
+      </c>
+      <c r="P24" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>319</v>
+      </c>
+      <c r="R24" t="s">
+        <v>323</v>
+      </c>
+      <c r="S24" t="s">
+        <v>332</v>
+      </c>
+      <c r="T24" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" t="s">
+        <v>173</v>
+      </c>
+      <c r="E25" t="s">
+        <v>196</v>
+      </c>
+      <c r="F25" t="s">
+        <v>250</v>
+      </c>
+      <c r="G25" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H25" t="s">
+        <v>263</v>
+      </c>
+      <c r="I25" t="s">
+        <v>309</v>
+      </c>
+      <c r="L25" t="s">
+        <v>314</v>
+      </c>
+      <c r="M25" t="s">
+        <v>315</v>
+      </c>
+      <c r="N25" t="s">
+        <v>316</v>
+      </c>
+      <c r="O25" t="s">
+        <v>317</v>
+      </c>
+      <c r="P25" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>319</v>
+      </c>
+      <c r="R25" t="s">
+        <v>323</v>
+      </c>
+      <c r="S25" t="s">
+        <v>332</v>
+      </c>
+      <c r="T25" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" t="s">
+        <v>197</v>
+      </c>
+      <c r="F26" t="s">
+        <v>251</v>
+      </c>
+      <c r="G26" s="2">
+        <v>45877</v>
+      </c>
+      <c r="H26" t="s">
+        <v>264</v>
+      </c>
+      <c r="I26" t="s">
+        <v>309</v>
+      </c>
+      <c r="L26" t="s">
+        <v>314</v>
+      </c>
+      <c r="M26" t="s">
+        <v>315</v>
+      </c>
+      <c r="N26" t="s">
+        <v>316</v>
+      </c>
+      <c r="O26" t="s">
+        <v>317</v>
+      </c>
+      <c r="P26" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" t="s">
+        <v>323</v>
+      </c>
+      <c r="S26" t="s">
+        <v>332</v>
+      </c>
+      <c r="T26" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s">
+        <v>172</v>
+      </c>
+      <c r="D27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" t="s">
+        <v>250</v>
+      </c>
+      <c r="G27" s="2">
+        <v>45884</v>
+      </c>
+      <c r="H27" t="s">
+        <v>265</v>
+      </c>
+      <c r="I27" t="s">
+        <v>309</v>
+      </c>
+      <c r="L27" t="s">
+        <v>314</v>
+      </c>
+      <c r="M27" t="s">
+        <v>315</v>
+      </c>
+      <c r="N27" t="s">
+        <v>316</v>
+      </c>
+      <c r="O27" t="s">
+        <v>317</v>
+      </c>
+      <c r="P27" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>319</v>
+      </c>
+      <c r="R27" t="s">
+        <v>323</v>
+      </c>
+      <c r="S27" t="s">
+        <v>332</v>
+      </c>
+      <c r="T27" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" t="s">
+        <v>199</v>
+      </c>
+      <c r="F28" t="s">
+        <v>250</v>
+      </c>
+      <c r="G28" s="2">
+        <v>45870</v>
+      </c>
+      <c r="H28" t="s">
+        <v>266</v>
+      </c>
+      <c r="I28" t="s">
+        <v>309</v>
+      </c>
+      <c r="L28" t="s">
+        <v>314</v>
+      </c>
+      <c r="M28" t="s">
+        <v>315</v>
+      </c>
+      <c r="N28" t="s">
+        <v>316</v>
+      </c>
+      <c r="O28" t="s">
+        <v>317</v>
+      </c>
+      <c r="P28" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>319</v>
+      </c>
+      <c r="R28" t="s">
+        <v>323</v>
+      </c>
+      <c r="S28" t="s">
+        <v>332</v>
+      </c>
+      <c r="T28" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" t="s">
+        <v>172</v>
+      </c>
+      <c r="D29" t="s">
+        <v>173</v>
+      </c>
+      <c r="E29" t="s">
+        <v>200</v>
+      </c>
+      <c r="F29" t="s">
+        <v>250</v>
+      </c>
+      <c r="G29" s="2">
+        <v>45871</v>
+      </c>
+      <c r="H29" t="s">
+        <v>267</v>
+      </c>
+      <c r="I29" t="s">
+        <v>309</v>
+      </c>
+      <c r="L29" t="s">
+        <v>314</v>
+      </c>
+      <c r="M29" t="s">
+        <v>315</v>
+      </c>
+      <c r="N29" t="s">
+        <v>316</v>
+      </c>
+      <c r="O29" t="s">
+        <v>317</v>
+      </c>
+      <c r="P29" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>319</v>
+      </c>
+      <c r="R29" t="s">
+        <v>323</v>
+      </c>
+      <c r="S29" t="s">
+        <v>332</v>
+      </c>
+      <c r="T29" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" t="s">
+        <v>172</v>
+      </c>
+      <c r="D30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" t="s">
+        <v>201</v>
+      </c>
+      <c r="F30" t="s">
+        <v>250</v>
+      </c>
+      <c r="G30" s="2">
+        <v>45873</v>
+      </c>
+      <c r="H30" t="s">
+        <v>268</v>
+      </c>
+      <c r="I30" t="s">
+        <v>309</v>
+      </c>
+      <c r="L30" t="s">
+        <v>314</v>
+      </c>
+      <c r="M30" t="s">
+        <v>315</v>
+      </c>
+      <c r="N30" t="s">
+        <v>316</v>
+      </c>
+      <c r="O30" t="s">
+        <v>317</v>
+      </c>
+      <c r="P30" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>319</v>
+      </c>
+      <c r="R30" t="s">
+        <v>323</v>
+      </c>
+      <c r="S30" t="s">
+        <v>332</v>
+      </c>
+      <c r="T30" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" t="s">
+        <v>250</v>
+      </c>
+      <c r="G31" s="2">
+        <v>45874</v>
+      </c>
+      <c r="H31" t="s">
+        <v>269</v>
+      </c>
+      <c r="I31" t="s">
+        <v>309</v>
+      </c>
+      <c r="L31" t="s">
+        <v>314</v>
+      </c>
+      <c r="M31" t="s">
+        <v>315</v>
+      </c>
+      <c r="N31" t="s">
+        <v>316</v>
+      </c>
+      <c r="O31" t="s">
+        <v>317</v>
+      </c>
+      <c r="P31" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>319</v>
+      </c>
+      <c r="R31" t="s">
+        <v>323</v>
+      </c>
+      <c r="S31" t="s">
+        <v>332</v>
+      </c>
+      <c r="T31" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="A32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" t="s">
+        <v>172</v>
+      </c>
+      <c r="D32" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" t="s">
+        <v>203</v>
+      </c>
+      <c r="F32" t="s">
+        <v>250</v>
+      </c>
+      <c r="G32" s="2">
+        <v>45876</v>
+      </c>
+      <c r="H32" t="s">
+        <v>270</v>
+      </c>
+      <c r="I32" t="s">
+        <v>309</v>
+      </c>
+      <c r="L32" t="s">
+        <v>314</v>
+      </c>
+      <c r="M32" t="s">
+        <v>315</v>
+      </c>
+      <c r="N32" t="s">
+        <v>316</v>
+      </c>
+      <c r="O32" t="s">
+        <v>317</v>
+      </c>
+      <c r="P32" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>319</v>
+      </c>
+      <c r="R32" t="s">
+        <v>323</v>
+      </c>
+      <c r="S32" t="s">
+        <v>332</v>
+      </c>
+      <c r="T32" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33" t="s">
+        <v>173</v>
+      </c>
+      <c r="E33" t="s">
+        <v>204</v>
+      </c>
+      <c r="F33" t="s">
+        <v>250</v>
+      </c>
+      <c r="G33" s="2">
+        <v>45877</v>
+      </c>
+      <c r="H33" t="s">
+        <v>271</v>
+      </c>
+      <c r="I33" t="s">
+        <v>309</v>
+      </c>
+      <c r="L33" t="s">
+        <v>314</v>
+      </c>
+      <c r="M33" t="s">
+        <v>315</v>
+      </c>
+      <c r="N33" t="s">
+        <v>316</v>
+      </c>
+      <c r="O33" t="s">
+        <v>317</v>
+      </c>
+      <c r="P33" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>319</v>
+      </c>
+      <c r="R33" t="s">
+        <v>323</v>
+      </c>
+      <c r="S33" t="s">
+        <v>332</v>
+      </c>
+      <c r="T33" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
+      <c r="A34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" t="s">
+        <v>205</v>
+      </c>
+      <c r="F34" t="s">
+        <v>251</v>
+      </c>
+      <c r="G34" s="2">
+        <v>45872</v>
+      </c>
+      <c r="H34" t="s">
+        <v>272</v>
+      </c>
+      <c r="I34" t="s">
+        <v>309</v>
+      </c>
+      <c r="L34" t="s">
+        <v>314</v>
+      </c>
+      <c r="M34" t="s">
+        <v>315</v>
+      </c>
+      <c r="N34" t="s">
+        <v>316</v>
+      </c>
+      <c r="O34" t="s">
+        <v>317</v>
+      </c>
+      <c r="P34" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>319</v>
+      </c>
+      <c r="R34" t="s">
+        <v>323</v>
+      </c>
+      <c r="S34" t="s">
+        <v>332</v>
+      </c>
+      <c r="T34" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" t="s">
+        <v>172</v>
+      </c>
+      <c r="D35" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" t="s">
+        <v>206</v>
+      </c>
+      <c r="F35" t="s">
+        <v>250</v>
+      </c>
+      <c r="G35" s="2">
+        <v>45879</v>
+      </c>
+      <c r="H35" t="s">
+        <v>273</v>
+      </c>
+      <c r="I35" t="s">
+        <v>309</v>
+      </c>
+      <c r="L35" t="s">
+        <v>314</v>
+      </c>
+      <c r="M35" t="s">
+        <v>315</v>
+      </c>
+      <c r="N35" t="s">
+        <v>316</v>
+      </c>
+      <c r="O35" t="s">
+        <v>317</v>
+      </c>
+      <c r="P35" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>319</v>
+      </c>
+      <c r="R35" t="s">
+        <v>323</v>
+      </c>
+      <c r="S35" t="s">
+        <v>332</v>
+      </c>
+      <c r="T35" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" t="s">
+        <v>207</v>
+      </c>
+      <c r="F36" t="s">
+        <v>250</v>
+      </c>
+      <c r="G36" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H36" t="s">
+        <v>274</v>
+      </c>
+      <c r="I36" t="s">
+        <v>309</v>
+      </c>
+      <c r="L36" t="s">
+        <v>314</v>
+      </c>
+      <c r="M36" t="s">
+        <v>315</v>
+      </c>
+      <c r="N36" t="s">
+        <v>316</v>
+      </c>
+      <c r="O36" t="s">
+        <v>317</v>
+      </c>
+      <c r="P36" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>319</v>
+      </c>
+      <c r="R36" t="s">
+        <v>323</v>
+      </c>
+      <c r="S36" t="s">
+        <v>332</v>
+      </c>
+      <c r="T36" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" t="s">
+        <v>172</v>
+      </c>
+      <c r="D37" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" t="s">
+        <v>208</v>
+      </c>
+      <c r="F37" t="s">
+        <v>251</v>
+      </c>
+      <c r="G37" s="2">
+        <v>45875</v>
+      </c>
+      <c r="H37" t="s">
+        <v>275</v>
+      </c>
+      <c r="I37" t="s">
+        <v>309</v>
+      </c>
+      <c r="L37" t="s">
+        <v>314</v>
+      </c>
+      <c r="M37" t="s">
+        <v>315</v>
+      </c>
+      <c r="N37" t="s">
+        <v>316</v>
+      </c>
+      <c r="O37" t="s">
+        <v>317</v>
+      </c>
+      <c r="P37" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>319</v>
+      </c>
+      <c r="R37" t="s">
+        <v>323</v>
+      </c>
+      <c r="S37" t="s">
+        <v>332</v>
+      </c>
+      <c r="T37" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" t="s">
+        <v>172</v>
+      </c>
+      <c r="D38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" t="s">
+        <v>209</v>
+      </c>
+      <c r="F38" t="s">
+        <v>250</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H38" t="s">
+        <v>276</v>
+      </c>
+      <c r="I38" t="s">
+        <v>309</v>
+      </c>
+      <c r="L38" t="s">
+        <v>314</v>
+      </c>
+      <c r="M38" t="s">
+        <v>315</v>
+      </c>
+      <c r="N38" t="s">
+        <v>316</v>
+      </c>
+      <c r="O38" t="s">
+        <v>317</v>
+      </c>
+      <c r="P38" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>319</v>
+      </c>
+      <c r="R38" t="s">
+        <v>323</v>
+      </c>
+      <c r="S38" t="s">
+        <v>332</v>
+      </c>
+      <c r="T38" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" t="s">
+        <v>172</v>
+      </c>
+      <c r="D39" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" t="s">
+        <v>210</v>
+      </c>
+      <c r="F39" t="s">
+        <v>250</v>
+      </c>
+      <c r="G39" s="2">
+        <v>45883</v>
+      </c>
+      <c r="H39" t="s">
+        <v>277</v>
+      </c>
+      <c r="I39" t="s">
+        <v>309</v>
+      </c>
+      <c r="L39" t="s">
+        <v>314</v>
+      </c>
+      <c r="M39" t="s">
+        <v>315</v>
+      </c>
+      <c r="N39" t="s">
+        <v>316</v>
+      </c>
+      <c r="O39" t="s">
+        <v>317</v>
+      </c>
+      <c r="P39" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>319</v>
+      </c>
+      <c r="R39" t="s">
+        <v>323</v>
+      </c>
+      <c r="S39" t="s">
+        <v>332</v>
+      </c>
+      <c r="T39" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
+      <c r="A40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" t="s">
+        <v>211</v>
+      </c>
+      <c r="F40" t="s">
+        <v>251</v>
+      </c>
+      <c r="G40" s="2">
+        <v>45878</v>
+      </c>
+      <c r="H40" t="s">
+        <v>278</v>
+      </c>
+      <c r="I40" t="s">
+        <v>309</v>
+      </c>
+      <c r="L40" t="s">
+        <v>314</v>
+      </c>
+      <c r="M40" t="s">
+        <v>315</v>
+      </c>
+      <c r="N40" t="s">
+        <v>316</v>
+      </c>
+      <c r="O40" t="s">
+        <v>317</v>
+      </c>
+      <c r="P40" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>319</v>
+      </c>
+      <c r="R40" t="s">
+        <v>323</v>
+      </c>
+      <c r="S40" t="s">
+        <v>332</v>
+      </c>
+      <c r="T40" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" t="s">
+        <v>172</v>
+      </c>
+      <c r="D41" t="s">
+        <v>173</v>
+      </c>
+      <c r="E41" t="s">
+        <v>212</v>
+      </c>
+      <c r="F41" t="s">
+        <v>250</v>
+      </c>
+      <c r="G41" s="2">
+        <v>45871</v>
+      </c>
+      <c r="H41" t="s">
+        <v>279</v>
+      </c>
+      <c r="I41" t="s">
+        <v>309</v>
+      </c>
+      <c r="L41" t="s">
+        <v>314</v>
+      </c>
+      <c r="M41" t="s">
+        <v>315</v>
+      </c>
+      <c r="N41" t="s">
+        <v>316</v>
+      </c>
+      <c r="O41" t="s">
+        <v>317</v>
+      </c>
+      <c r="P41" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>319</v>
+      </c>
+      <c r="R41" t="s">
+        <v>323</v>
+      </c>
+      <c r="S41" t="s">
+        <v>332</v>
+      </c>
+      <c r="T41" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
+      <c r="A42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42" t="s">
+        <v>135</v>
+      </c>
+      <c r="C42" t="s">
+        <v>172</v>
+      </c>
+      <c r="D42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" t="s">
+        <v>213</v>
+      </c>
+      <c r="F42" t="s">
+        <v>250</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45872</v>
+      </c>
+      <c r="H42" t="s">
+        <v>280</v>
+      </c>
+      <c r="I42" t="s">
+        <v>309</v>
+      </c>
+      <c r="L42" t="s">
+        <v>314</v>
+      </c>
+      <c r="M42" t="s">
+        <v>315</v>
+      </c>
+      <c r="N42" t="s">
+        <v>316</v>
+      </c>
+      <c r="O42" t="s">
+        <v>317</v>
+      </c>
+      <c r="P42" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>319</v>
+      </c>
+      <c r="R42" t="s">
+        <v>323</v>
+      </c>
+      <c r="S42" t="s">
+        <v>332</v>
+      </c>
+      <c r="T42" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" t="s">
+        <v>214</v>
+      </c>
+      <c r="F43" t="s">
+        <v>250</v>
+      </c>
+      <c r="G43" s="2">
+        <v>45874</v>
+      </c>
+      <c r="H43" t="s">
+        <v>281</v>
+      </c>
+      <c r="I43" t="s">
+        <v>309</v>
+      </c>
+      <c r="L43" t="s">
+        <v>314</v>
+      </c>
+      <c r="M43" t="s">
+        <v>315</v>
+      </c>
+      <c r="N43" t="s">
+        <v>316</v>
+      </c>
+      <c r="O43" t="s">
+        <v>317</v>
+      </c>
+      <c r="P43" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>319</v>
+      </c>
+      <c r="R43" t="s">
+        <v>323</v>
+      </c>
+      <c r="S43" t="s">
+        <v>332</v>
+      </c>
+      <c r="T43" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" t="s">
+        <v>215</v>
+      </c>
+      <c r="F44" t="s">
+        <v>250</v>
+      </c>
+      <c r="G44" s="2">
+        <v>45875</v>
+      </c>
+      <c r="H44" t="s">
+        <v>282</v>
+      </c>
+      <c r="I44" t="s">
+        <v>309</v>
+      </c>
+      <c r="L44" t="s">
+        <v>314</v>
+      </c>
+      <c r="M44" t="s">
+        <v>315</v>
+      </c>
+      <c r="N44" t="s">
+        <v>316</v>
+      </c>
+      <c r="O44" t="s">
+        <v>317</v>
+      </c>
+      <c r="P44" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>319</v>
+      </c>
+      <c r="R44" t="s">
+        <v>323</v>
+      </c>
+      <c r="S44" t="s">
+        <v>332</v>
+      </c>
+      <c r="T44" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
+      <c r="A45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" t="s">
+        <v>216</v>
+      </c>
+      <c r="F45" t="s">
+        <v>250</v>
+      </c>
+      <c r="G45" s="2">
+        <v>45870</v>
+      </c>
+      <c r="H45" t="s">
+        <v>283</v>
+      </c>
+      <c r="I45" t="s">
+        <v>311</v>
+      </c>
+      <c r="L45" t="s">
+        <v>314</v>
+      </c>
+      <c r="M45" t="s">
+        <v>315</v>
+      </c>
+      <c r="N45" t="s">
+        <v>316</v>
+      </c>
+      <c r="O45" t="s">
+        <v>317</v>
+      </c>
+      <c r="P45" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>319</v>
+      </c>
+      <c r="R45" t="s">
+        <v>327</v>
+      </c>
+      <c r="S45" t="s">
+        <v>333</v>
+      </c>
+      <c r="T45" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
+      <c r="A46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46" t="s">
+        <v>172</v>
+      </c>
+      <c r="D46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" t="s">
+        <v>217</v>
+      </c>
+      <c r="F46" t="s">
+        <v>250</v>
+      </c>
+      <c r="G46" s="2">
+        <v>45872</v>
+      </c>
+      <c r="H46" t="s">
+        <v>284</v>
+      </c>
+      <c r="I46" t="s">
+        <v>312</v>
+      </c>
+      <c r="J46" t="s">
+        <v>313</v>
+      </c>
+      <c r="L46" t="s">
+        <v>314</v>
+      </c>
+      <c r="M46" t="s">
+        <v>315</v>
+      </c>
+      <c r="N46" t="s">
+        <v>316</v>
+      </c>
+      <c r="O46" t="s">
+        <v>317</v>
+      </c>
+      <c r="P46" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>319</v>
+      </c>
+      <c r="R46" t="s">
+        <v>328</v>
+      </c>
+      <c r="S46" t="s">
+        <v>336</v>
+      </c>
+      <c r="T46" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" t="s">
+        <v>172</v>
+      </c>
+      <c r="D47" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" t="s">
+        <v>218</v>
+      </c>
+      <c r="F47" t="s">
+        <v>250</v>
+      </c>
+      <c r="G47" s="2">
+        <v>45871</v>
+      </c>
+      <c r="H47" t="s">
+        <v>285</v>
+      </c>
+      <c r="I47" t="s">
+        <v>312</v>
+      </c>
+      <c r="L47" t="s">
+        <v>314</v>
+      </c>
+      <c r="M47" t="s">
+        <v>315</v>
+      </c>
+      <c r="N47" t="s">
+        <v>316</v>
+      </c>
+      <c r="O47" t="s">
+        <v>317</v>
+      </c>
+      <c r="P47" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>321</v>
+      </c>
+      <c r="R47" t="s">
+        <v>323</v>
+      </c>
+      <c r="S47" t="s">
+        <v>332</v>
+      </c>
+      <c r="T47" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
+      <c r="A48" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" t="s">
+        <v>141</v>
+      </c>
+      <c r="C48" t="s">
+        <v>172</v>
+      </c>
+      <c r="D48" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" t="s">
+        <v>219</v>
+      </c>
+      <c r="F48" t="s">
+        <v>250</v>
+      </c>
+      <c r="G48" s="2">
+        <v>45872</v>
+      </c>
+      <c r="H48" t="s">
+        <v>286</v>
+      </c>
+      <c r="I48" t="s">
+        <v>312</v>
+      </c>
+      <c r="L48" t="s">
+        <v>314</v>
+      </c>
+      <c r="M48" t="s">
+        <v>315</v>
+      </c>
+      <c r="N48" t="s">
+        <v>316</v>
+      </c>
+      <c r="O48" t="s">
+        <v>317</v>
+      </c>
+      <c r="P48" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>319</v>
+      </c>
+      <c r="R48" t="s">
+        <v>323</v>
+      </c>
+      <c r="S48" t="s">
+        <v>332</v>
+      </c>
+      <c r="T48" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
+      <c r="A49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" t="s">
+        <v>172</v>
+      </c>
+      <c r="D49" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" t="s">
+        <v>220</v>
+      </c>
+      <c r="F49" t="s">
+        <v>250</v>
+      </c>
+      <c r="G49" s="2">
+        <v>45873</v>
+      </c>
+      <c r="H49" t="s">
+        <v>287</v>
+      </c>
+      <c r="I49" t="s">
+        <v>312</v>
+      </c>
+      <c r="L49" t="s">
+        <v>314</v>
+      </c>
+      <c r="M49" t="s">
+        <v>315</v>
+      </c>
+      <c r="N49" t="s">
+        <v>316</v>
+      </c>
+      <c r="O49" t="s">
+        <v>317</v>
+      </c>
+      <c r="P49" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>322</v>
+      </c>
+      <c r="R49" t="s">
+        <v>323</v>
+      </c>
+      <c r="S49" t="s">
+        <v>332</v>
+      </c>
+      <c r="T49" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
+      <c r="A50" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" t="s">
+        <v>172</v>
+      </c>
+      <c r="D50" t="s">
+        <v>173</v>
+      </c>
+      <c r="E50" t="s">
+        <v>221</v>
+      </c>
+      <c r="F50" t="s">
+        <v>250</v>
+      </c>
+      <c r="G50" s="2">
+        <v>45874</v>
+      </c>
+      <c r="H50" t="s">
+        <v>288</v>
+      </c>
+      <c r="I50" t="s">
+        <v>312</v>
+      </c>
+      <c r="L50" t="s">
+        <v>314</v>
+      </c>
+      <c r="M50" t="s">
+        <v>315</v>
+      </c>
+      <c r="N50" t="s">
+        <v>316</v>
+      </c>
+      <c r="O50" t="s">
+        <v>317</v>
+      </c>
+      <c r="P50" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>320</v>
+      </c>
+      <c r="R50" t="s">
+        <v>323</v>
+      </c>
+      <c r="S50" t="s">
+        <v>332</v>
+      </c>
+      <c r="T50" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20">
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" t="s">
+        <v>144</v>
+      </c>
+      <c r="C51" t="s">
+        <v>172</v>
+      </c>
+      <c r="D51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" t="s">
+        <v>222</v>
+      </c>
+      <c r="F51" t="s">
+        <v>250</v>
+      </c>
+      <c r="G51" s="2">
+        <v>45875</v>
+      </c>
+      <c r="H51" t="s">
+        <v>289</v>
+      </c>
+      <c r="I51" t="s">
+        <v>312</v>
+      </c>
+      <c r="L51" t="s">
+        <v>314</v>
+      </c>
+      <c r="M51" t="s">
+        <v>315</v>
+      </c>
+      <c r="N51" t="s">
+        <v>316</v>
+      </c>
+      <c r="O51" t="s">
+        <v>317</v>
+      </c>
+      <c r="P51" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>321</v>
+      </c>
+      <c r="R51" t="s">
+        <v>323</v>
+      </c>
+      <c r="S51" t="s">
+        <v>332</v>
+      </c>
+      <c r="T51" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" t="s">
+        <v>173</v>
+      </c>
+      <c r="E52" t="s">
+        <v>223</v>
+      </c>
+      <c r="F52" t="s">
+        <v>250</v>
+      </c>
+      <c r="G52" s="2">
+        <v>45876</v>
+      </c>
+      <c r="H52" t="s">
+        <v>283</v>
+      </c>
+      <c r="I52" t="s">
+        <v>312</v>
+      </c>
+      <c r="L52" t="s">
+        <v>314</v>
+      </c>
+      <c r="M52" t="s">
+        <v>315</v>
+      </c>
+      <c r="N52" t="s">
+        <v>316</v>
+      </c>
+      <c r="O52" t="s">
+        <v>317</v>
+      </c>
+      <c r="P52" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>319</v>
+      </c>
+      <c r="R52" t="s">
+        <v>323</v>
+      </c>
+      <c r="S52" t="s">
+        <v>332</v>
+      </c>
+      <c r="T52" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
+      <c r="A53" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" t="s">
+        <v>146</v>
+      </c>
+      <c r="C53" t="s">
+        <v>172</v>
+      </c>
+      <c r="D53" t="s">
+        <v>173</v>
+      </c>
+      <c r="E53" t="s">
+        <v>224</v>
+      </c>
+      <c r="F53" t="s">
+        <v>250</v>
+      </c>
+      <c r="G53" s="2">
+        <v>45877</v>
+      </c>
+      <c r="H53" t="s">
+        <v>290</v>
+      </c>
+      <c r="I53" t="s">
+        <v>312</v>
+      </c>
+      <c r="L53" t="s">
+        <v>314</v>
+      </c>
+      <c r="M53" t="s">
+        <v>315</v>
+      </c>
+      <c r="N53" t="s">
+        <v>316</v>
+      </c>
+      <c r="O53" t="s">
+        <v>317</v>
+      </c>
+      <c r="P53" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>322</v>
+      </c>
+      <c r="R53" t="s">
+        <v>323</v>
+      </c>
+      <c r="S53" t="s">
+        <v>332</v>
+      </c>
+      <c r="T53" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
+      <c r="A54" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" t="s">
+        <v>147</v>
+      </c>
+      <c r="C54" t="s">
+        <v>172</v>
+      </c>
+      <c r="D54" t="s">
+        <v>173</v>
+      </c>
+      <c r="E54" t="s">
+        <v>225</v>
+      </c>
+      <c r="F54" t="s">
+        <v>250</v>
+      </c>
+      <c r="G54" s="2">
+        <v>45878</v>
+      </c>
+      <c r="H54" t="s">
+        <v>291</v>
+      </c>
+      <c r="I54" t="s">
+        <v>312</v>
+      </c>
+      <c r="L54" t="s">
+        <v>314</v>
+      </c>
+      <c r="M54" t="s">
+        <v>315</v>
+      </c>
+      <c r="N54" t="s">
+        <v>316</v>
+      </c>
+      <c r="O54" t="s">
+        <v>317</v>
+      </c>
+      <c r="P54" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>320</v>
+      </c>
+      <c r="R54" t="s">
+        <v>323</v>
+      </c>
+      <c r="S54" t="s">
+        <v>332</v>
+      </c>
+      <c r="T54" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
+      <c r="A55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" t="s">
+        <v>148</v>
+      </c>
+      <c r="C55" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" t="s">
+        <v>173</v>
+      </c>
+      <c r="E55" t="s">
+        <v>226</v>
+      </c>
+      <c r="F55" t="s">
+        <v>250</v>
+      </c>
+      <c r="G55" s="2">
+        <v>45879</v>
+      </c>
+      <c r="H55" t="s">
+        <v>292</v>
+      </c>
+      <c r="I55" t="s">
+        <v>312</v>
+      </c>
+      <c r="L55" t="s">
+        <v>314</v>
+      </c>
+      <c r="M55" t="s">
+        <v>315</v>
+      </c>
+      <c r="N55" t="s">
+        <v>316</v>
+      </c>
+      <c r="O55" t="s">
+        <v>317</v>
+      </c>
+      <c r="P55" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>321</v>
+      </c>
+      <c r="R55" t="s">
+        <v>323</v>
+      </c>
+      <c r="S55" t="s">
+        <v>332</v>
+      </c>
+      <c r="T55" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
+      <c r="A56" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" t="s">
+        <v>172</v>
+      </c>
+      <c r="D56" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" t="s">
+        <v>227</v>
+      </c>
+      <c r="F56" t="s">
+        <v>250</v>
+      </c>
+      <c r="G56" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H56" t="s">
+        <v>256</v>
+      </c>
+      <c r="I56" t="s">
+        <v>312</v>
+      </c>
+      <c r="L56" t="s">
+        <v>314</v>
+      </c>
+      <c r="M56" t="s">
+        <v>315</v>
+      </c>
+      <c r="N56" t="s">
+        <v>316</v>
+      </c>
+      <c r="O56" t="s">
+        <v>317</v>
+      </c>
+      <c r="P56" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>319</v>
+      </c>
+      <c r="R56" t="s">
+        <v>323</v>
+      </c>
+      <c r="S56" t="s">
+        <v>332</v>
+      </c>
+      <c r="T56" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20">
+      <c r="A57" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" t="s">
+        <v>172</v>
+      </c>
+      <c r="D57" t="s">
+        <v>173</v>
+      </c>
+      <c r="E57" t="s">
+        <v>228</v>
+      </c>
+      <c r="F57" t="s">
+        <v>250</v>
+      </c>
+      <c r="G57" s="2">
+        <v>45881</v>
+      </c>
+      <c r="H57" t="s">
+        <v>293</v>
+      </c>
+      <c r="I57" t="s">
+        <v>312</v>
+      </c>
+      <c r="L57" t="s">
+        <v>314</v>
+      </c>
+      <c r="M57" t="s">
+        <v>315</v>
+      </c>
+      <c r="N57" t="s">
+        <v>316</v>
+      </c>
+      <c r="O57" t="s">
+        <v>317</v>
+      </c>
+      <c r="P57" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>322</v>
+      </c>
+      <c r="R57" t="s">
+        <v>323</v>
+      </c>
+      <c r="S57" t="s">
+        <v>332</v>
+      </c>
+      <c r="T57" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
+      <c r="A58" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58" t="s">
+        <v>151</v>
+      </c>
+      <c r="C58" t="s">
+        <v>172</v>
+      </c>
+      <c r="D58" t="s">
+        <v>173</v>
+      </c>
+      <c r="E58" t="s">
+        <v>229</v>
+      </c>
+      <c r="F58" t="s">
+        <v>250</v>
+      </c>
+      <c r="G58" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H58" t="s">
+        <v>294</v>
+      </c>
+      <c r="I58" t="s">
+        <v>312</v>
+      </c>
+      <c r="L58" t="s">
+        <v>314</v>
+      </c>
+      <c r="M58" t="s">
+        <v>315</v>
+      </c>
+      <c r="N58" t="s">
+        <v>316</v>
+      </c>
+      <c r="O58" t="s">
+        <v>317</v>
+      </c>
+      <c r="P58" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>320</v>
+      </c>
+      <c r="R58" t="s">
+        <v>323</v>
+      </c>
+      <c r="S58" t="s">
+        <v>332</v>
+      </c>
+      <c r="T58" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20">
+      <c r="A59" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" t="s">
+        <v>172</v>
+      </c>
+      <c r="D59" t="s">
+        <v>173</v>
+      </c>
+      <c r="E59" t="s">
+        <v>230</v>
+      </c>
+      <c r="F59" t="s">
+        <v>250</v>
+      </c>
+      <c r="G59" s="2">
+        <v>45883</v>
+      </c>
+      <c r="H59" t="s">
+        <v>295</v>
+      </c>
+      <c r="I59" t="s">
+        <v>312</v>
+      </c>
+      <c r="L59" t="s">
+        <v>314</v>
+      </c>
+      <c r="M59" t="s">
+        <v>315</v>
+      </c>
+      <c r="N59" t="s">
+        <v>316</v>
+      </c>
+      <c r="O59" t="s">
+        <v>317</v>
+      </c>
+      <c r="P59" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>321</v>
+      </c>
+      <c r="R59" t="s">
+        <v>323</v>
+      </c>
+      <c r="S59" t="s">
+        <v>332</v>
+      </c>
+      <c r="T59" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C60" t="s">
+        <v>172</v>
+      </c>
+      <c r="D60" t="s">
+        <v>173</v>
+      </c>
+      <c r="E60" t="s">
+        <v>231</v>
+      </c>
+      <c r="F60" t="s">
+        <v>250</v>
+      </c>
+      <c r="G60" s="2">
+        <v>45884</v>
+      </c>
+      <c r="H60" t="s">
+        <v>284</v>
+      </c>
+      <c r="I60" t="s">
+        <v>312</v>
+      </c>
+      <c r="L60" t="s">
+        <v>314</v>
+      </c>
+      <c r="M60" t="s">
+        <v>315</v>
+      </c>
+      <c r="N60" t="s">
+        <v>316</v>
+      </c>
+      <c r="O60" t="s">
+        <v>317</v>
+      </c>
+      <c r="P60" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>319</v>
+      </c>
+      <c r="R60" t="s">
+        <v>323</v>
+      </c>
+      <c r="S60" t="s">
+        <v>332</v>
+      </c>
+      <c r="T60" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20">
+      <c r="A61" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" t="s">
+        <v>154</v>
+      </c>
+      <c r="C61" t="s">
+        <v>172</v>
+      </c>
+      <c r="D61" t="s">
+        <v>173</v>
+      </c>
+      <c r="E61" t="s">
+        <v>232</v>
+      </c>
+      <c r="F61" t="s">
+        <v>250</v>
+      </c>
+      <c r="G61" s="2">
+        <v>45885</v>
+      </c>
+      <c r="H61" t="s">
+        <v>296</v>
+      </c>
+      <c r="I61" t="s">
+        <v>312</v>
+      </c>
+      <c r="L61" t="s">
+        <v>314</v>
+      </c>
+      <c r="M61" t="s">
+        <v>315</v>
+      </c>
+      <c r="N61" t="s">
+        <v>316</v>
+      </c>
+      <c r="O61" t="s">
+        <v>317</v>
+      </c>
+      <c r="P61" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>322</v>
+      </c>
+      <c r="R61" t="s">
+        <v>323</v>
+      </c>
+      <c r="S61" t="s">
+        <v>332</v>
+      </c>
+      <c r="T61" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20">
+      <c r="A62" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" t="s">
+        <v>155</v>
+      </c>
+      <c r="C62" t="s">
+        <v>172</v>
+      </c>
+      <c r="D62" t="s">
+        <v>173</v>
+      </c>
+      <c r="E62" t="s">
+        <v>233</v>
+      </c>
+      <c r="F62" t="s">
+        <v>250</v>
+      </c>
+      <c r="G62" s="2">
+        <v>45886</v>
+      </c>
+      <c r="H62" t="s">
+        <v>297</v>
+      </c>
+      <c r="I62" t="s">
+        <v>312</v>
+      </c>
+      <c r="L62" t="s">
+        <v>314</v>
+      </c>
+      <c r="M62" t="s">
+        <v>315</v>
+      </c>
+      <c r="N62" t="s">
+        <v>316</v>
+      </c>
+      <c r="O62" t="s">
+        <v>317</v>
+      </c>
+      <c r="P62" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>320</v>
+      </c>
+      <c r="R62" t="s">
+        <v>323</v>
+      </c>
+      <c r="S62" t="s">
+        <v>332</v>
+      </c>
+      <c r="T62" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20">
+      <c r="A63" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63" t="s">
+        <v>156</v>
+      </c>
+      <c r="C63" t="s">
+        <v>172</v>
+      </c>
+      <c r="D63" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" t="s">
+        <v>234</v>
+      </c>
+      <c r="F63" t="s">
+        <v>250</v>
+      </c>
+      <c r="G63" s="2">
+        <v>45887</v>
+      </c>
+      <c r="H63" t="s">
+        <v>298</v>
+      </c>
+      <c r="I63" t="s">
+        <v>312</v>
+      </c>
+      <c r="L63" t="s">
+        <v>314</v>
+      </c>
+      <c r="M63" t="s">
+        <v>315</v>
+      </c>
+      <c r="N63" t="s">
+        <v>316</v>
+      </c>
+      <c r="O63" t="s">
+        <v>317</v>
+      </c>
+      <c r="P63" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>321</v>
+      </c>
+      <c r="R63" t="s">
+        <v>323</v>
+      </c>
+      <c r="S63" t="s">
+        <v>332</v>
+      </c>
+      <c r="T63" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20">
+      <c r="A64" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" t="s">
+        <v>172</v>
+      </c>
+      <c r="D64" t="s">
+        <v>173</v>
+      </c>
+      <c r="E64" t="s">
+        <v>235</v>
+      </c>
+      <c r="F64" t="s">
+        <v>250</v>
+      </c>
+      <c r="G64" s="2">
+        <v>45888</v>
+      </c>
+      <c r="H64" t="s">
+        <v>299</v>
+      </c>
+      <c r="I64" t="s">
+        <v>312</v>
+      </c>
+      <c r="L64" t="s">
+        <v>314</v>
+      </c>
+      <c r="M64" t="s">
+        <v>315</v>
+      </c>
+      <c r="N64" t="s">
+        <v>316</v>
+      </c>
+      <c r="O64" t="s">
+        <v>317</v>
+      </c>
+      <c r="P64" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>319</v>
+      </c>
+      <c r="R64" t="s">
+        <v>323</v>
+      </c>
+      <c r="S64" t="s">
+        <v>332</v>
+      </c>
+      <c r="T64" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
+      <c r="A65" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65" t="s">
+        <v>158</v>
+      </c>
+      <c r="C65" t="s">
+        <v>172</v>
+      </c>
+      <c r="D65" t="s">
+        <v>173</v>
+      </c>
+      <c r="E65" t="s">
+        <v>236</v>
+      </c>
+      <c r="F65" t="s">
+        <v>250</v>
+      </c>
+      <c r="G65" s="2">
+        <v>45889</v>
+      </c>
+      <c r="H65" t="s">
+        <v>300</v>
+      </c>
+      <c r="I65" t="s">
+        <v>312</v>
+      </c>
+      <c r="L65" t="s">
+        <v>314</v>
+      </c>
+      <c r="M65" t="s">
+        <v>315</v>
+      </c>
+      <c r="N65" t="s">
+        <v>316</v>
+      </c>
+      <c r="O65" t="s">
+        <v>317</v>
+      </c>
+      <c r="P65" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>322</v>
+      </c>
+      <c r="R65" t="s">
+        <v>323</v>
+      </c>
+      <c r="S65" t="s">
+        <v>332</v>
+      </c>
+      <c r="T65" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" t="s">
+        <v>159</v>
+      </c>
+      <c r="C66" t="s">
+        <v>172</v>
+      </c>
+      <c r="D66" t="s">
+        <v>173</v>
+      </c>
+      <c r="E66" t="s">
+        <v>237</v>
+      </c>
+      <c r="F66" t="s">
+        <v>250</v>
+      </c>
+      <c r="G66" s="2">
+        <v>45877</v>
+      </c>
+      <c r="H66" t="s">
+        <v>258</v>
+      </c>
+      <c r="I66" t="s">
+        <v>311</v>
+      </c>
+      <c r="K66" t="s">
+        <v>313</v>
+      </c>
+      <c r="L66" t="s">
+        <v>314</v>
+      </c>
+      <c r="M66" t="s">
+        <v>315</v>
+      </c>
+      <c r="N66" t="s">
+        <v>316</v>
+      </c>
+      <c r="O66" t="s">
+        <v>317</v>
+      </c>
+      <c r="P66" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>319</v>
+      </c>
+      <c r="R66" t="s">
+        <v>323</v>
+      </c>
+      <c r="S66" t="s">
+        <v>332</v>
+      </c>
+      <c r="T66" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20">
+      <c r="A67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B67" t="s">
+        <v>159</v>
+      </c>
+      <c r="C67" t="s">
+        <v>172</v>
+      </c>
+      <c r="D67" t="s">
+        <v>173</v>
+      </c>
+      <c r="E67" t="s">
+        <v>237</v>
+      </c>
+      <c r="F67" t="s">
+        <v>250</v>
+      </c>
+      <c r="G67" s="2">
+        <v>45877</v>
+      </c>
+      <c r="H67" t="s">
+        <v>255</v>
+      </c>
+      <c r="I67" t="s">
+        <v>311</v>
+      </c>
+      <c r="K67" t="s">
+        <v>313</v>
+      </c>
+      <c r="L67" t="s">
+        <v>314</v>
+      </c>
+      <c r="M67" t="s">
+        <v>315</v>
+      </c>
+      <c r="N67" t="s">
+        <v>316</v>
+      </c>
+      <c r="O67" t="s">
+        <v>317</v>
+      </c>
+      <c r="P67" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>319</v>
+      </c>
+      <c r="R67" t="s">
+        <v>329</v>
+      </c>
+      <c r="S67" t="s">
+        <v>335</v>
+      </c>
+      <c r="T67" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" t="s">
+        <v>172</v>
+      </c>
+      <c r="D68" t="s">
+        <v>173</v>
+      </c>
+      <c r="E68" t="s">
+        <v>238</v>
+      </c>
+      <c r="F68" t="s">
+        <v>250</v>
+      </c>
+      <c r="G68" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H68" t="s">
+        <v>258</v>
+      </c>
+      <c r="I68" t="s">
+        <v>311</v>
+      </c>
+      <c r="K68" t="s">
+        <v>313</v>
+      </c>
+      <c r="L68" t="s">
+        <v>314</v>
+      </c>
+      <c r="M68" t="s">
+        <v>315</v>
+      </c>
+      <c r="N68" t="s">
+        <v>316</v>
+      </c>
+      <c r="O68" t="s">
+        <v>317</v>
+      </c>
+      <c r="P68" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>319</v>
+      </c>
+      <c r="R68" t="s">
+        <v>323</v>
+      </c>
+      <c r="S68" t="s">
+        <v>332</v>
+      </c>
+      <c r="T68" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20">
+      <c r="A69" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" t="s">
+        <v>160</v>
+      </c>
+      <c r="C69" t="s">
+        <v>172</v>
+      </c>
+      <c r="D69" t="s">
+        <v>173</v>
+      </c>
+      <c r="E69" t="s">
+        <v>238</v>
+      </c>
+      <c r="F69" t="s">
+        <v>250</v>
+      </c>
+      <c r="G69" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H69" t="s">
+        <v>255</v>
+      </c>
+      <c r="I69" t="s">
+        <v>311</v>
+      </c>
+      <c r="K69" t="s">
+        <v>313</v>
+      </c>
+      <c r="L69" t="s">
+        <v>314</v>
+      </c>
+      <c r="M69" t="s">
+        <v>315</v>
+      </c>
+      <c r="N69" t="s">
+        <v>316</v>
+      </c>
+      <c r="O69" t="s">
+        <v>317</v>
+      </c>
+      <c r="P69" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>319</v>
+      </c>
+      <c r="R69" t="s">
+        <v>329</v>
+      </c>
+      <c r="S69" t="s">
+        <v>335</v>
+      </c>
+      <c r="T69" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" t="s">
+        <v>161</v>
+      </c>
+      <c r="C70" t="s">
+        <v>172</v>
+      </c>
+      <c r="D70" t="s">
+        <v>173</v>
+      </c>
+      <c r="E70" t="s">
+        <v>239</v>
+      </c>
+      <c r="F70" t="s">
+        <v>250</v>
+      </c>
+      <c r="G70" s="2">
+        <v>45883</v>
+      </c>
+      <c r="H70" t="s">
+        <v>258</v>
+      </c>
+      <c r="I70" t="s">
+        <v>311</v>
+      </c>
+      <c r="K70" t="s">
+        <v>313</v>
+      </c>
+      <c r="L70" t="s">
+        <v>314</v>
+      </c>
+      <c r="M70" t="s">
+        <v>315</v>
+      </c>
+      <c r="N70" t="s">
+        <v>316</v>
+      </c>
+      <c r="O70" t="s">
+        <v>317</v>
+      </c>
+      <c r="P70" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>319</v>
+      </c>
+      <c r="R70" t="s">
+        <v>323</v>
+      </c>
+      <c r="S70" t="s">
+        <v>332</v>
+      </c>
+      <c r="T70" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20">
+      <c r="A71" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" t="s">
+        <v>161</v>
+      </c>
+      <c r="C71" t="s">
+        <v>172</v>
+      </c>
+      <c r="D71" t="s">
+        <v>173</v>
+      </c>
+      <c r="E71" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" t="s">
+        <v>250</v>
+      </c>
+      <c r="G71" s="2">
+        <v>45883</v>
+      </c>
+      <c r="H71" t="s">
+        <v>255</v>
+      </c>
+      <c r="I71" t="s">
+        <v>311</v>
+      </c>
+      <c r="K71" t="s">
+        <v>313</v>
+      </c>
+      <c r="L71" t="s">
+        <v>314</v>
+      </c>
+      <c r="M71" t="s">
+        <v>315</v>
+      </c>
+      <c r="N71" t="s">
+        <v>316</v>
+      </c>
+      <c r="O71" t="s">
+        <v>317</v>
+      </c>
+      <c r="P71" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>319</v>
+      </c>
+      <c r="R71" t="s">
+        <v>329</v>
+      </c>
+      <c r="S71" t="s">
+        <v>335</v>
+      </c>
+      <c r="T71" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20">
+      <c r="A72" t="s">
+        <v>86</v>
+      </c>
+      <c r="B72" t="s">
+        <v>162</v>
+      </c>
+      <c r="C72" t="s">
+        <v>172</v>
+      </c>
+      <c r="D72" t="s">
+        <v>173</v>
+      </c>
+      <c r="E72" t="s">
+        <v>240</v>
+      </c>
+      <c r="F72" t="s">
+        <v>250</v>
+      </c>
+      <c r="G72" s="2">
+        <v>45872</v>
+      </c>
+      <c r="H72" t="s">
+        <v>258</v>
+      </c>
+      <c r="I72" t="s">
+        <v>311</v>
+      </c>
+      <c r="K72" t="s">
+        <v>313</v>
+      </c>
+      <c r="L72" t="s">
+        <v>314</v>
+      </c>
+      <c r="M72" t="s">
+        <v>315</v>
+      </c>
+      <c r="N72" t="s">
+        <v>316</v>
+      </c>
+      <c r="O72" t="s">
+        <v>317</v>
+      </c>
+      <c r="P72" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>319</v>
+      </c>
+      <c r="R72" t="s">
+        <v>323</v>
+      </c>
+      <c r="S72" t="s">
+        <v>332</v>
+      </c>
+      <c r="T72" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20">
+      <c r="A73" t="s">
+        <v>86</v>
+      </c>
+      <c r="B73" t="s">
+        <v>162</v>
+      </c>
+      <c r="C73" t="s">
+        <v>172</v>
+      </c>
+      <c r="D73" t="s">
+        <v>173</v>
+      </c>
+      <c r="E73" t="s">
+        <v>240</v>
+      </c>
+      <c r="F73" t="s">
+        <v>250</v>
+      </c>
+      <c r="G73" s="2">
+        <v>45872</v>
+      </c>
+      <c r="H73" t="s">
+        <v>255</v>
+      </c>
+      <c r="I73" t="s">
+        <v>311</v>
+      </c>
+      <c r="K73" t="s">
+        <v>313</v>
+      </c>
+      <c r="L73" t="s">
+        <v>314</v>
+      </c>
+      <c r="M73" t="s">
+        <v>315</v>
+      </c>
+      <c r="N73" t="s">
+        <v>316</v>
+      </c>
+      <c r="O73" t="s">
+        <v>317</v>
+      </c>
+      <c r="P73" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>319</v>
+      </c>
+      <c r="R73" t="s">
+        <v>329</v>
+      </c>
+      <c r="S73" t="s">
+        <v>335</v>
+      </c>
+      <c r="T73" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20">
+      <c r="A74" t="s">
+        <v>87</v>
+      </c>
+      <c r="B74" t="s">
+        <v>163</v>
+      </c>
+      <c r="C74" t="s">
+        <v>172</v>
+      </c>
+      <c r="D74" t="s">
+        <v>173</v>
+      </c>
+      <c r="E74" t="s">
+        <v>241</v>
+      </c>
+      <c r="F74" t="s">
+        <v>250</v>
+      </c>
+      <c r="G74" s="2">
+        <v>45875</v>
+      </c>
+      <c r="H74" t="s">
+        <v>258</v>
+      </c>
+      <c r="I74" t="s">
+        <v>311</v>
+      </c>
+      <c r="K74" t="s">
+        <v>313</v>
+      </c>
+      <c r="L74" t="s">
+        <v>314</v>
+      </c>
+      <c r="M74" t="s">
+        <v>315</v>
+      </c>
+      <c r="N74" t="s">
+        <v>316</v>
+      </c>
+      <c r="O74" t="s">
+        <v>317</v>
+      </c>
+      <c r="P74" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>319</v>
+      </c>
+      <c r="R74" t="s">
+        <v>323</v>
+      </c>
+      <c r="S74" t="s">
+        <v>332</v>
+      </c>
+      <c r="T74" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20">
+      <c r="A75" t="s">
+        <v>87</v>
+      </c>
+      <c r="B75" t="s">
+        <v>163</v>
+      </c>
+      <c r="C75" t="s">
+        <v>172</v>
+      </c>
+      <c r="D75" t="s">
+        <v>173</v>
+      </c>
+      <c r="E75" t="s">
+        <v>241</v>
+      </c>
+      <c r="F75" t="s">
+        <v>250</v>
+      </c>
+      <c r="G75" s="2">
+        <v>45875</v>
+      </c>
+      <c r="H75" t="s">
+        <v>255</v>
+      </c>
+      <c r="I75" t="s">
+        <v>311</v>
+      </c>
+      <c r="K75" t="s">
+        <v>313</v>
+      </c>
+      <c r="L75" t="s">
+        <v>314</v>
+      </c>
+      <c r="M75" t="s">
+        <v>315</v>
+      </c>
+      <c r="N75" t="s">
+        <v>316</v>
+      </c>
+      <c r="O75" t="s">
+        <v>317</v>
+      </c>
+      <c r="P75" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>319</v>
+      </c>
+      <c r="R75" t="s">
+        <v>329</v>
+      </c>
+      <c r="S75" t="s">
+        <v>335</v>
+      </c>
+      <c r="T75" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20">
+      <c r="A76" t="s">
+        <v>88</v>
+      </c>
+      <c r="B76" t="s">
+        <v>164</v>
+      </c>
+      <c r="C76" t="s">
+        <v>172</v>
+      </c>
+      <c r="D76" t="s">
+        <v>173</v>
+      </c>
+      <c r="E76" t="s">
+        <v>242</v>
+      </c>
+      <c r="F76" t="s">
+        <v>250</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45886</v>
+      </c>
+      <c r="H76" t="s">
+        <v>301</v>
+      </c>
+      <c r="I76" t="s">
+        <v>309</v>
+      </c>
+      <c r="L76" t="s">
+        <v>314</v>
+      </c>
+      <c r="M76" t="s">
+        <v>315</v>
+      </c>
+      <c r="N76" t="s">
+        <v>316</v>
+      </c>
+      <c r="O76" t="s">
+        <v>317</v>
+      </c>
+      <c r="P76" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>319</v>
+      </c>
+      <c r="R76" t="s">
+        <v>329</v>
+      </c>
+      <c r="S76" t="s">
+        <v>335</v>
+      </c>
+      <c r="T76" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20">
+      <c r="A77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B77" t="s">
+        <v>165</v>
+      </c>
+      <c r="C77" t="s">
+        <v>172</v>
+      </c>
+      <c r="D77" t="s">
+        <v>173</v>
+      </c>
+      <c r="E77" t="s">
+        <v>243</v>
+      </c>
+      <c r="F77" t="s">
+        <v>250</v>
+      </c>
+      <c r="G77" s="2">
+        <v>45889</v>
+      </c>
+      <c r="H77" t="s">
+        <v>302</v>
+      </c>
+      <c r="I77" t="s">
+        <v>309</v>
+      </c>
+      <c r="L77" t="s">
+        <v>314</v>
+      </c>
+      <c r="M77" t="s">
+        <v>315</v>
+      </c>
+      <c r="N77" t="s">
+        <v>316</v>
+      </c>
+      <c r="O77" t="s">
+        <v>317</v>
+      </c>
+      <c r="P77" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>319</v>
+      </c>
+      <c r="R77" t="s">
+        <v>326</v>
+      </c>
+      <c r="S77" t="s">
+        <v>335</v>
+      </c>
+      <c r="T77" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20">
+      <c r="A78" t="s">
+        <v>90</v>
+      </c>
+      <c r="B78" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" t="s">
+        <v>172</v>
+      </c>
+      <c r="D78" t="s">
+        <v>173</v>
+      </c>
+      <c r="E78" t="s">
+        <v>244</v>
+      </c>
+      <c r="F78" t="s">
+        <v>250</v>
+      </c>
+      <c r="G78" s="2">
+        <v>45870</v>
+      </c>
+      <c r="H78" t="s">
+        <v>303</v>
+      </c>
+      <c r="I78" t="s">
+        <v>309</v>
+      </c>
+      <c r="L78" t="s">
+        <v>314</v>
+      </c>
+      <c r="M78" t="s">
+        <v>315</v>
+      </c>
+      <c r="N78" t="s">
+        <v>316</v>
+      </c>
+      <c r="O78" t="s">
+        <v>317</v>
+      </c>
+      <c r="P78" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>319</v>
+      </c>
+      <c r="R78" t="s">
+        <v>330</v>
+      </c>
+      <c r="S78" t="s">
+        <v>336</v>
+      </c>
+      <c r="T78" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20">
+      <c r="A79" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" t="s">
+        <v>167</v>
+      </c>
+      <c r="C79" t="s">
+        <v>172</v>
+      </c>
+      <c r="D79" t="s">
+        <v>173</v>
+      </c>
+      <c r="E79" t="s">
+        <v>245</v>
+      </c>
+      <c r="F79" t="s">
+        <v>250</v>
+      </c>
+      <c r="G79" s="2">
+        <v>45873</v>
+      </c>
+      <c r="H79" t="s">
+        <v>304</v>
+      </c>
+      <c r="I79" t="s">
+        <v>309</v>
+      </c>
+      <c r="L79" t="s">
+        <v>314</v>
+      </c>
+      <c r="M79" t="s">
+        <v>315</v>
+      </c>
+      <c r="N79" t="s">
+        <v>316</v>
+      </c>
+      <c r="O79" t="s">
+        <v>317</v>
+      </c>
+      <c r="P79" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>319</v>
+      </c>
+      <c r="R79" t="s">
+        <v>323</v>
+      </c>
+      <c r="S79" t="s">
+        <v>332</v>
+      </c>
+      <c r="T79" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20">
+      <c r="A80" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" t="s">
+        <v>168</v>
+      </c>
+      <c r="C80" t="s">
+        <v>172</v>
+      </c>
+      <c r="D80" t="s">
+        <v>173</v>
+      </c>
+      <c r="E80" t="s">
+        <v>246</v>
+      </c>
+      <c r="F80" t="s">
+        <v>250</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45876</v>
+      </c>
+      <c r="H80" t="s">
+        <v>305</v>
+      </c>
+      <c r="I80" t="s">
+        <v>309</v>
+      </c>
+      <c r="L80" t="s">
+        <v>314</v>
+      </c>
+      <c r="M80" t="s">
+        <v>315</v>
+      </c>
+      <c r="N80" t="s">
+        <v>316</v>
+      </c>
+      <c r="O80" t="s">
+        <v>317</v>
+      </c>
+      <c r="P80" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>319</v>
+      </c>
+      <c r="R80" t="s">
+        <v>331</v>
+      </c>
+      <c r="S80" t="s">
+        <v>337</v>
+      </c>
+      <c r="T80" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20">
+      <c r="A81" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" t="s">
+        <v>169</v>
+      </c>
+      <c r="C81" t="s">
+        <v>172</v>
+      </c>
+      <c r="D81" t="s">
+        <v>173</v>
+      </c>
+      <c r="E81" t="s">
+        <v>247</v>
+      </c>
+      <c r="F81" t="s">
+        <v>250</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H81" t="s">
+        <v>306</v>
+      </c>
+      <c r="I81" t="s">
+        <v>309</v>
+      </c>
+      <c r="L81" t="s">
+        <v>314</v>
+      </c>
+      <c r="M81" t="s">
+        <v>315</v>
+      </c>
+      <c r="N81" t="s">
+        <v>316</v>
+      </c>
+      <c r="O81" t="s">
+        <v>317</v>
+      </c>
+      <c r="P81" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>319</v>
+      </c>
+      <c r="R81" t="s">
+        <v>329</v>
+      </c>
+      <c r="S81" t="s">
+        <v>335</v>
+      </c>
+      <c r="T81" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20">
+      <c r="A82" t="s">
+        <v>93</v>
+      </c>
+      <c r="B82" t="s">
+        <v>169</v>
+      </c>
+      <c r="C82" t="s">
+        <v>172</v>
+      </c>
+      <c r="D82" t="s">
+        <v>173</v>
+      </c>
+      <c r="E82" t="s">
+        <v>247</v>
+      </c>
+      <c r="F82" t="s">
+        <v>250</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H82" t="s">
+        <v>306</v>
+      </c>
+      <c r="I82" t="s">
+        <v>309</v>
+      </c>
+      <c r="L82" t="s">
+        <v>314</v>
+      </c>
+      <c r="M82" t="s">
+        <v>315</v>
+      </c>
+      <c r="N82" t="s">
+        <v>316</v>
+      </c>
+      <c r="O82" t="s">
+        <v>317</v>
+      </c>
+      <c r="P82" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>319</v>
+      </c>
+      <c r="R82" t="s">
+        <v>326</v>
+      </c>
+      <c r="S82" t="s">
+        <v>335</v>
+      </c>
+      <c r="T82" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20">
+      <c r="A83" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" t="s">
+        <v>172</v>
+      </c>
+      <c r="D83" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" t="s">
+        <v>248</v>
+      </c>
+      <c r="F83" t="s">
+        <v>250</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H83" t="s">
+        <v>307</v>
+      </c>
+      <c r="I83" t="s">
+        <v>309</v>
+      </c>
+      <c r="L83" t="s">
+        <v>314</v>
+      </c>
+      <c r="M83" t="s">
+        <v>315</v>
+      </c>
+      <c r="N83" t="s">
+        <v>316</v>
+      </c>
+      <c r="O83" t="s">
+        <v>317</v>
+      </c>
+      <c r="P83" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>319</v>
+      </c>
+      <c r="R83" t="s">
+        <v>328</v>
+      </c>
+      <c r="S83" t="s">
+        <v>336</v>
+      </c>
+      <c r="T83" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20">
+      <c r="A84" t="s">
+        <v>94</v>
+      </c>
+      <c r="B84" t="s">
+        <v>170</v>
+      </c>
+      <c r="C84" t="s">
+        <v>172</v>
+      </c>
+      <c r="D84" t="s">
+        <v>173</v>
+      </c>
+      <c r="E84" t="s">
+        <v>248</v>
+      </c>
+      <c r="F84" t="s">
+        <v>250</v>
+      </c>
+      <c r="G84" s="2">
+        <v>45882</v>
+      </c>
+      <c r="H84" t="s">
+        <v>307</v>
+      </c>
+      <c r="I84" t="s">
+        <v>309</v>
+      </c>
+      <c r="L84" t="s">
+        <v>314</v>
+      </c>
+      <c r="M84" t="s">
+        <v>315</v>
+      </c>
+      <c r="N84" t="s">
+        <v>316</v>
+      </c>
+      <c r="O84" t="s">
+        <v>317</v>
+      </c>
+      <c r="P84" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>319</v>
+      </c>
+      <c r="R84" t="s">
+        <v>330</v>
+      </c>
+      <c r="S84" t="s">
+        <v>336</v>
+      </c>
+      <c r="T84" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20">
+      <c r="A85" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" t="s">
+        <v>172</v>
+      </c>
+      <c r="D85" t="s">
+        <v>173</v>
+      </c>
+      <c r="E85" t="s">
+        <v>249</v>
+      </c>
+      <c r="F85" t="s">
+        <v>250</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45885</v>
+      </c>
+      <c r="H85" t="s">
+        <v>308</v>
+      </c>
+      <c r="I85" t="s">
+        <v>309</v>
+      </c>
+      <c r="L85" t="s">
+        <v>314</v>
+      </c>
+      <c r="M85" t="s">
+        <v>315</v>
+      </c>
+      <c r="N85" t="s">
+        <v>316</v>
+      </c>
+      <c r="O85" t="s">
+        <v>317</v>
+      </c>
+      <c r="P85" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>319</v>
+      </c>
+      <c r="R85" t="s">
+        <v>323</v>
+      </c>
+      <c r="S85" t="s">
+        <v>332</v>
+      </c>
+      <c r="T85" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20">
+      <c r="A86" t="s">
+        <v>95</v>
+      </c>
+      <c r="B86" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" t="s">
+        <v>172</v>
+      </c>
+      <c r="D86" t="s">
+        <v>173</v>
+      </c>
+      <c r="E86" t="s">
+        <v>249</v>
+      </c>
+      <c r="F86" t="s">
+        <v>250</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45885</v>
+      </c>
+      <c r="H86" t="s">
+        <v>308</v>
+      </c>
+      <c r="I86" t="s">
+        <v>309</v>
+      </c>
+      <c r="L86" t="s">
+        <v>314</v>
+      </c>
+      <c r="M86" t="s">
+        <v>315</v>
+      </c>
+      <c r="N86" t="s">
+        <v>316</v>
+      </c>
+      <c r="O86" t="s">
+        <v>317</v>
+      </c>
+      <c r="P86" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>319</v>
+      </c>
+      <c r="R86" t="s">
+        <v>331</v>
+      </c>
+      <c r="S86" t="s">
+        <v>337</v>
+      </c>
+      <c r="T86" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="352">
   <si>
     <t>Código Produto</t>
   </si>
@@ -265,21 +265,18 @@
     <t>PROD300049</t>
   </si>
   <si>
-    <t>PROD400004</t>
-  </si>
-  <si>
-    <t>PROD400005</t>
-  </si>
-  <si>
     <t>PROD400006</t>
   </si>
   <si>
+    <t>PROD400007</t>
+  </si>
+  <si>
+    <t>PROD400008</t>
+  </si>
+  <si>
     <t>PROD400009</t>
   </si>
   <si>
-    <t>PROD4000010</t>
-  </si>
-  <si>
     <t>PROD500007</t>
   </si>
   <si>
@@ -493,21 +490,18 @@
     <t>Produto de Teste - Processo 300049</t>
   </si>
   <si>
-    <t>Produto de Teste - Processo 400004</t>
-  </si>
-  <si>
-    <t>Produto de Teste - Processo 400005</t>
-  </si>
-  <si>
     <t>Produto de Teste - Processo 400006</t>
   </si>
   <si>
+    <t>Produto de Teste - Processo 400007</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400008</t>
+  </si>
+  <si>
     <t>Produto de Teste - Processo 400009</t>
   </si>
   <si>
-    <t>Produto de Teste - Processo 4000010</t>
-  </si>
-  <si>
     <t>Produto de Teste - Processo 500007</t>
   </si>
   <si>
@@ -727,21 +721,18 @@
     <t>300049</t>
   </si>
   <si>
-    <t>400004</t>
-  </si>
-  <si>
-    <t>400005</t>
-  </si>
-  <si>
     <t>400006</t>
   </si>
   <si>
+    <t>400007</t>
+  </si>
+  <si>
+    <t>400008</t>
+  </si>
+  <si>
     <t>400009</t>
   </si>
   <si>
-    <t>4000010</t>
-  </si>
-  <si>
     <t>500007</t>
   </si>
   <si>
@@ -919,6 +910,18 @@
     <t>34500</t>
   </si>
   <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>11000</t>
+  </si>
+  <si>
+    <t>16000</t>
+  </si>
+  <si>
+    <t>13000</t>
+  </si>
+  <si>
     <t>50000</t>
   </si>
   <si>
@@ -943,19 +946,34 @@
     <t>37500</t>
   </si>
   <si>
-    <t>Alessandro Cappi</t>
-  </si>
-  <si>
-    <t>André Caramello</t>
-  </si>
-  <si>
-    <t>Mateus Machado</t>
-  </si>
-  <si>
-    <t>Andrey Andrade</t>
-  </si>
-  <si>
-    <t>André Camargo</t>
+    <t>ANDREY.ANDRADE</t>
+  </si>
+  <si>
+    <t>SAMANTA</t>
+  </si>
+  <si>
+    <t>JULIANO</t>
+  </si>
+  <si>
+    <t>DENER.MARTINS</t>
+  </si>
+  <si>
+    <t>ROSANA.MARTINS</t>
+  </si>
+  <si>
+    <t>RAFAELA.MEIRELLES</t>
+  </si>
+  <si>
+    <t>ROSILENE</t>
+  </si>
+  <si>
+    <t>MATEUS BORRO MACHADO</t>
+  </si>
+  <si>
+    <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
+  </si>
+  <si>
+    <t>LEONARDO DO CARMO</t>
   </si>
   <si>
     <t>Industrial</t>
@@ -1003,15 +1021,24 @@
     <t>QED</t>
   </si>
   <si>
+    <t>EXO</t>
+  </si>
+  <si>
+    <t>MicroClip</t>
+  </si>
+  <si>
     <t>YSI</t>
   </si>
   <si>
+    <t>Panther</t>
+  </si>
+  <si>
+    <t>IQ Standard</t>
+  </si>
+  <si>
     <t>Thermo</t>
   </si>
   <si>
-    <t>MicroClip</t>
-  </si>
-  <si>
     <t>Analisador Fixo</t>
   </si>
   <si>
@@ -1027,7 +1054,13 @@
     <t>Sistema Remediação</t>
   </si>
   <si>
+    <t>Sonda Multiparâmetros</t>
+  </si>
+  <si>
     <t>Detector Portátil</t>
+  </si>
+  <si>
+    <t>Medidor de Vazão Fixo</t>
   </si>
   <si>
     <t>SSO</t>
@@ -1398,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T86"/>
+  <dimension ref="A1:T84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1468,55 +1501,52 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" t="s">
         <v>172</v>
       </c>
-      <c r="D2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E2" t="s">
-        <v>174</v>
-      </c>
       <c r="F2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G2" s="2">
         <v>45870</v>
       </c>
       <c r="H2" t="s">
-        <v>252</v>
-      </c>
-      <c r="I2" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="L2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S2" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T2" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -1524,55 +1554,52 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" t="s">
         <v>173</v>
       </c>
-      <c r="E3" t="s">
-        <v>175</v>
-      </c>
       <c r="F3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G3" s="2">
         <v>45875</v>
       </c>
       <c r="H3" t="s">
-        <v>253</v>
-      </c>
-      <c r="I3" t="s">
-        <v>309</v>
+        <v>250</v>
       </c>
       <c r="L3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M3" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N3" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R3" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S3" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T3" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -1580,55 +1607,52 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G4" s="2">
         <v>45880</v>
       </c>
       <c r="H4" t="s">
-        <v>254</v>
-      </c>
-      <c r="I4" t="s">
-        <v>309</v>
+        <v>251</v>
       </c>
       <c r="L4" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M4" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N4" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O4" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P4" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q4" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R4" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S4" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T4" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -1636,55 +1660,52 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G5" s="2">
         <v>45880</v>
       </c>
       <c r="H5" t="s">
-        <v>255</v>
-      </c>
-      <c r="I5" t="s">
-        <v>310</v>
+        <v>252</v>
       </c>
       <c r="L5" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M5" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N5" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O5" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P5" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q5" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R5" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="S5" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="T5" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1692,55 +1713,52 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G6" s="2">
         <v>45885</v>
       </c>
       <c r="H6" t="s">
-        <v>256</v>
-      </c>
-      <c r="I6" t="s">
-        <v>309</v>
+        <v>253</v>
       </c>
       <c r="L6" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M6" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N6" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O6" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P6" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q6" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="R6" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="S6" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="T6" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1748,55 +1766,52 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G7" s="2">
         <v>45872</v>
       </c>
       <c r="H7" t="s">
-        <v>257</v>
-      </c>
-      <c r="I7" t="s">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="L7" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M7" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N7" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O7" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P7" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q7" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R7" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S7" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T7" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1804,55 +1819,52 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F8" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G8" s="2">
         <v>45888</v>
       </c>
       <c r="H8" t="s">
-        <v>252</v>
-      </c>
-      <c r="I8" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="L8" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N8" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O8" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P8" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q8" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R8" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S8" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T8" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1860,55 +1872,52 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G9" s="2">
         <v>45871</v>
       </c>
       <c r="H9" t="s">
-        <v>258</v>
-      </c>
-      <c r="I9" t="s">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="L9" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M9" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N9" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O9" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P9" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q9" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R9" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S9" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T9" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1916,55 +1925,52 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F10" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G10" s="2">
         <v>45872</v>
       </c>
       <c r="H10" t="s">
-        <v>258</v>
-      </c>
-      <c r="I10" t="s">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="L10" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M10" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N10" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P10" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q10" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R10" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S10" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T10" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1972,55 +1978,52 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G11" s="2">
         <v>45873</v>
       </c>
       <c r="H11" t="s">
-        <v>258</v>
-      </c>
-      <c r="I11" t="s">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="L11" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M11" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N11" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O11" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P11" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q11" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R11" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S11" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T11" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -2028,55 +2031,52 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F12" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G12" s="2">
         <v>45874</v>
       </c>
       <c r="H12" t="s">
-        <v>258</v>
-      </c>
-      <c r="I12" t="s">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="L12" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M12" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N12" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O12" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P12" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q12" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R12" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S12" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T12" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -2084,55 +2084,52 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E13" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F13" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G13" s="2">
         <v>45875</v>
       </c>
       <c r="H13" t="s">
-        <v>258</v>
-      </c>
-      <c r="I13" t="s">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="L13" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M13" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N13" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O13" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P13" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q13" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R13" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S13" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T13" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -2140,55 +2137,52 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F14" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G14" s="2">
         <v>45876</v>
       </c>
       <c r="H14" t="s">
-        <v>258</v>
-      </c>
-      <c r="I14" t="s">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c r="L14" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M14" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N14" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O14" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P14" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q14" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R14" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S14" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T14" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -2196,55 +2190,52 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F15" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G15" s="2">
         <v>45872</v>
       </c>
       <c r="H15" t="s">
-        <v>252</v>
-      </c>
-      <c r="I15" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="L15" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M15" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N15" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O15" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P15" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q15" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R15" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="S15" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="T15" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -2252,55 +2243,52 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D16" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G16" s="2">
         <v>45873</v>
       </c>
       <c r="H16" t="s">
-        <v>252</v>
-      </c>
-      <c r="I16" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="L16" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M16" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N16" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O16" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P16" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q16" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R16" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="S16" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="T16" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -2308,55 +2296,52 @@
         <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E17" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F17" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G17" s="2">
         <v>45874</v>
       </c>
       <c r="H17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I17" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="L17" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M17" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N17" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O17" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P17" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q17" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R17" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="S17" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="T17" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:20">
@@ -2364,55 +2349,52 @@
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E18" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F18" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G18" s="2">
         <v>45875</v>
       </c>
       <c r="H18" t="s">
-        <v>252</v>
-      </c>
-      <c r="I18" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="L18" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M18" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N18" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O18" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P18" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q18" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R18" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="S18" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="T18" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:20">
@@ -2420,55 +2402,52 @@
         <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D19" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E19" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F19" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G19" s="2">
         <v>45876</v>
       </c>
       <c r="H19" t="s">
-        <v>252</v>
-      </c>
-      <c r="I19" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="L19" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M19" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N19" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O19" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P19" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q19" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R19" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="S19" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="T19" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:20">
@@ -2476,55 +2455,52 @@
         <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F20" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G20" s="2">
         <v>45877</v>
       </c>
       <c r="H20" t="s">
-        <v>252</v>
-      </c>
-      <c r="I20" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="L20" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M20" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N20" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O20" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P20" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q20" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R20" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="S20" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="T20" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:20">
@@ -2532,55 +2508,52 @@
         <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F21" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G21" s="2">
         <v>45878</v>
       </c>
       <c r="H21" t="s">
-        <v>259</v>
-      </c>
-      <c r="I21" t="s">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="L21" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M21" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N21" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O21" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P21" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q21" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R21" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S21" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T21" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -2588,55 +2561,52 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E22" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F22" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G22" s="2">
         <v>45879</v>
       </c>
       <c r="H22" t="s">
-        <v>260</v>
-      </c>
-      <c r="I22" t="s">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="L22" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M22" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N22" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O22" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P22" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q22" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R22" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S22" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T22" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -2644,55 +2614,52 @@
         <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E23" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F23" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G23" s="2">
         <v>45874</v>
       </c>
       <c r="H23" t="s">
-        <v>261</v>
-      </c>
-      <c r="I23" t="s">
-        <v>309</v>
+        <v>258</v>
       </c>
       <c r="L23" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M23" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N23" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O23" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P23" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q23" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R23" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S23" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T23" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -2700,55 +2667,52 @@
         <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F24" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G24" s="2">
         <v>45881</v>
       </c>
       <c r="H24" t="s">
-        <v>262</v>
-      </c>
-      <c r="I24" t="s">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="L24" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M24" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N24" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O24" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P24" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q24" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R24" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S24" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T24" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="1:20">
@@ -2756,55 +2720,52 @@
         <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D25" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E25" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F25" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G25" s="2">
         <v>45882</v>
       </c>
       <c r="H25" t="s">
-        <v>263</v>
-      </c>
-      <c r="I25" t="s">
-        <v>309</v>
+        <v>260</v>
       </c>
       <c r="L25" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M25" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N25" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O25" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P25" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q25" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R25" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S25" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T25" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="26" spans="1:20">
@@ -2812,55 +2773,52 @@
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E26" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F26" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G26" s="2">
         <v>45877</v>
       </c>
       <c r="H26" t="s">
-        <v>264</v>
-      </c>
-      <c r="I26" t="s">
-        <v>309</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M26" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N26" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O26" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P26" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q26" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R26" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S26" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T26" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" spans="1:20">
@@ -2868,55 +2826,52 @@
         <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F27" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G27" s="2">
         <v>45884</v>
       </c>
       <c r="H27" t="s">
-        <v>265</v>
-      </c>
-      <c r="I27" t="s">
-        <v>309</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M27" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N27" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O27" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P27" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q27" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R27" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S27" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T27" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -2924,55 +2879,52 @@
         <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F28" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G28" s="2">
         <v>45870</v>
       </c>
       <c r="H28" t="s">
-        <v>266</v>
-      </c>
-      <c r="I28" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="L28" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M28" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N28" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O28" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P28" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q28" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R28" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S28" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T28" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -2980,55 +2932,52 @@
         <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D29" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E29" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F29" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G29" s="2">
         <v>45871</v>
       </c>
       <c r="H29" t="s">
-        <v>267</v>
-      </c>
-      <c r="I29" t="s">
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="L29" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M29" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N29" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O29" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P29" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q29" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R29" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S29" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T29" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -3036,55 +2985,52 @@
         <v>47</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E30" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F30" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G30" s="2">
         <v>45873</v>
       </c>
       <c r="H30" t="s">
-        <v>268</v>
-      </c>
-      <c r="I30" t="s">
-        <v>309</v>
+        <v>265</v>
       </c>
       <c r="L30" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M30" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N30" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O30" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P30" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q30" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R30" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S30" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T30" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:20">
@@ -3092,55 +3038,52 @@
         <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D31" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E31" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F31" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G31" s="2">
         <v>45874</v>
       </c>
       <c r="H31" t="s">
-        <v>269</v>
-      </c>
-      <c r="I31" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="L31" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M31" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N31" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O31" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P31" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q31" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R31" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S31" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T31" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -3148,55 +3091,52 @@
         <v>49</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D32" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E32" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F32" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G32" s="2">
         <v>45876</v>
       </c>
       <c r="H32" t="s">
-        <v>270</v>
-      </c>
-      <c r="I32" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="L32" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M32" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N32" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O32" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P32" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q32" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R32" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S32" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T32" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" spans="1:20">
@@ -3204,55 +3144,52 @@
         <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D33" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E33" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F33" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G33" s="2">
         <v>45877</v>
       </c>
       <c r="H33" t="s">
-        <v>271</v>
-      </c>
-      <c r="I33" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="L33" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N33" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O33" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P33" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q33" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R33" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S33" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T33" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -3260,55 +3197,52 @@
         <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E34" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F34" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G34" s="2">
         <v>45872</v>
       </c>
       <c r="H34" t="s">
-        <v>272</v>
-      </c>
-      <c r="I34" t="s">
-        <v>309</v>
+        <v>269</v>
       </c>
       <c r="L34" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O34" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P34" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q34" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R34" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S34" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T34" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:20">
@@ -3316,55 +3250,52 @@
         <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D35" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E35" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F35" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G35" s="2">
         <v>45879</v>
       </c>
       <c r="H35" t="s">
-        <v>273</v>
-      </c>
-      <c r="I35" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="L35" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M35" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N35" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O35" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P35" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q35" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R35" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S35" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T35" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -3372,55 +3303,52 @@
         <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E36" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G36" s="2">
         <v>45880</v>
       </c>
       <c r="H36" t="s">
-        <v>274</v>
-      </c>
-      <c r="I36" t="s">
-        <v>309</v>
+        <v>271</v>
       </c>
       <c r="L36" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q36" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R36" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S36" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T36" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:20">
@@ -3428,55 +3356,52 @@
         <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F37" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G37" s="2">
         <v>45875</v>
       </c>
       <c r="H37" t="s">
-        <v>275</v>
-      </c>
-      <c r="I37" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="L37" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M37" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N37" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O37" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P37" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q37" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R37" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S37" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T37" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -3484,55 +3409,52 @@
         <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F38" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G38" s="2">
         <v>45882</v>
       </c>
       <c r="H38" t="s">
-        <v>276</v>
-      </c>
-      <c r="I38" t="s">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="L38" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M38" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N38" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O38" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P38" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q38" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R38" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S38" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T38" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -3540,55 +3462,52 @@
         <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D39" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E39" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F39" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G39" s="2">
         <v>45883</v>
       </c>
       <c r="H39" t="s">
-        <v>277</v>
-      </c>
-      <c r="I39" t="s">
-        <v>309</v>
+        <v>274</v>
       </c>
       <c r="L39" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N39" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O39" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P39" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q39" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R39" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S39" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T39" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" spans="1:20">
@@ -3596,55 +3515,52 @@
         <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D40" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E40" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F40" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G40" s="2">
         <v>45878</v>
       </c>
       <c r="H40" t="s">
-        <v>278</v>
-      </c>
-      <c r="I40" t="s">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="L40" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M40" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N40" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O40" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P40" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q40" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R40" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S40" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T40" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:20">
@@ -3652,55 +3568,52 @@
         <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E41" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F41" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G41" s="2">
         <v>45871</v>
       </c>
       <c r="H41" t="s">
-        <v>279</v>
-      </c>
-      <c r="I41" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="L41" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M41" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N41" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O41" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P41" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q41" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R41" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S41" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T41" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -3708,55 +3621,52 @@
         <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D42" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E42" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F42" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G42" s="2">
         <v>45872</v>
       </c>
       <c r="H42" t="s">
-        <v>280</v>
-      </c>
-      <c r="I42" t="s">
-        <v>309</v>
+        <v>277</v>
       </c>
       <c r="L42" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M42" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N42" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O42" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P42" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q42" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R42" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S42" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T42" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -3764,55 +3674,52 @@
         <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D43" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E43" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F43" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G43" s="2">
         <v>45874</v>
       </c>
       <c r="H43" t="s">
-        <v>281</v>
-      </c>
-      <c r="I43" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="L43" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M43" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N43" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O43" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P43" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q43" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R43" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S43" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T43" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -3820,55 +3727,52 @@
         <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C44" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D44" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E44" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F44" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G44" s="2">
         <v>45875</v>
       </c>
       <c r="H44" t="s">
-        <v>282</v>
-      </c>
-      <c r="I44" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="L44" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M44" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N44" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O44" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P44" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q44" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R44" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S44" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T44" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="1:20">
@@ -3876,55 +3780,58 @@
         <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D45" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E45" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F45" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G45" s="2">
         <v>45870</v>
       </c>
       <c r="H45" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I45" t="s">
-        <v>311</v>
+        <v>310</v>
+      </c>
+      <c r="J45" t="s">
+        <v>317</v>
       </c>
       <c r="L45" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N45" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O45" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P45" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q45" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R45" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="S45" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="T45" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -3932,58 +3839,58 @@
         <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D46" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E46" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F46" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G46" s="2">
         <v>45872</v>
       </c>
       <c r="H46" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I46" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J46" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L46" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M46" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N46" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O46" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P46" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q46" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R46" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="S46" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="T46" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -3991,55 +3898,52 @@
         <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D47" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E47" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G47" s="2">
         <v>45871</v>
       </c>
       <c r="H47" t="s">
-        <v>285</v>
-      </c>
-      <c r="I47" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="L47" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M47" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N47" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O47" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P47" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q47" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="R47" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="S47" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="T47" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -4047,55 +3951,58 @@
         <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D48" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E48" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F48" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G48" s="2">
         <v>45872</v>
       </c>
       <c r="H48" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I48" t="s">
-        <v>312</v>
+        <v>311</v>
+      </c>
+      <c r="J48" t="s">
+        <v>318</v>
       </c>
       <c r="L48" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M48" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N48" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O48" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P48" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q48" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R48" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="S48" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="T48" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -4103,55 +4010,55 @@
         <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E49" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F49" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G49" s="2">
         <v>45873</v>
       </c>
       <c r="H49" t="s">
-        <v>287</v>
-      </c>
-      <c r="I49" t="s">
-        <v>312</v>
+        <v>284</v>
+      </c>
+      <c r="J49" t="s">
+        <v>319</v>
       </c>
       <c r="L49" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N49" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O49" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P49" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q49" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="R49" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="S49" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="T49" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -4159,55 +4066,58 @@
         <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C50" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D50" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E50" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F50" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G50" s="2">
         <v>45874</v>
       </c>
       <c r="H50" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="I50" t="s">
         <v>312</v>
       </c>
+      <c r="J50" t="s">
+        <v>317</v>
+      </c>
       <c r="L50" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M50" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N50" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O50" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P50" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q50" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="R50" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="S50" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="T50" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" spans="1:20">
@@ -4215,55 +4125,52 @@
         <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D51" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E51" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F51" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G51" s="2">
         <v>45875</v>
       </c>
       <c r="H51" t="s">
-        <v>289</v>
-      </c>
-      <c r="I51" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="L51" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M51" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N51" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O51" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P51" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q51" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="R51" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="S51" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="T51" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52" spans="1:20">
@@ -4271,55 +4178,58 @@
         <v>69</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E52" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F52" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G52" s="2">
         <v>45876</v>
       </c>
       <c r="H52" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I52" t="s">
-        <v>312</v>
+        <v>313</v>
+      </c>
+      <c r="J52" t="s">
+        <v>318</v>
       </c>
       <c r="L52" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M52" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N52" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O52" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P52" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q52" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R52" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S52" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T52" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="53" spans="1:20">
@@ -4327,55 +4237,55 @@
         <v>70</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D53" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E53" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F53" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G53" s="2">
         <v>45877</v>
       </c>
       <c r="H53" t="s">
-        <v>290</v>
-      </c>
-      <c r="I53" t="s">
-        <v>312</v>
+        <v>287</v>
+      </c>
+      <c r="J53" t="s">
+        <v>317</v>
       </c>
       <c r="L53" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M53" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N53" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O53" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P53" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q53" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="R53" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="S53" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="T53" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -4383,55 +4293,58 @@
         <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C54" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D54" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E54" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F54" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G54" s="2">
         <v>45878</v>
       </c>
       <c r="H54" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="I54" t="s">
-        <v>312</v>
+        <v>314</v>
+      </c>
+      <c r="J54" t="s">
+        <v>317</v>
       </c>
       <c r="L54" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M54" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N54" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O54" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P54" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q54" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="R54" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="S54" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="T54" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="55" spans="1:20">
@@ -4439,55 +4352,52 @@
         <v>72</v>
       </c>
       <c r="B55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D55" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F55" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G55" s="2">
         <v>45879</v>
       </c>
       <c r="H55" t="s">
-        <v>292</v>
-      </c>
-      <c r="I55" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="L55" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M55" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N55" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O55" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P55" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q55" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="R55" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="S55" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="T55" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:20">
@@ -4495,55 +4405,58 @@
         <v>73</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D56" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E56" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F56" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G56" s="2">
         <v>45880</v>
       </c>
       <c r="H56" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I56" t="s">
-        <v>312</v>
+        <v>310</v>
+      </c>
+      <c r="J56" t="s">
+        <v>317</v>
       </c>
       <c r="L56" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M56" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N56" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O56" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P56" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q56" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R56" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="S56" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="T56" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57" spans="1:20">
@@ -4551,55 +4464,55 @@
         <v>74</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C57" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D57" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E57" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F57" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G57" s="2">
         <v>45881</v>
       </c>
       <c r="H57" t="s">
-        <v>293</v>
-      </c>
-      <c r="I57" t="s">
-        <v>312</v>
+        <v>290</v>
+      </c>
+      <c r="J57" t="s">
+        <v>319</v>
       </c>
       <c r="L57" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M57" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N57" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O57" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P57" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q57" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="R57" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="S57" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="T57" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -4607,55 +4520,58 @@
         <v>75</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C58" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D58" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E58" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F58" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G58" s="2">
         <v>45882</v>
       </c>
       <c r="H58" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I58" t="s">
-        <v>312</v>
+        <v>311</v>
+      </c>
+      <c r="J58" t="s">
+        <v>318</v>
       </c>
       <c r="L58" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M58" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N58" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O58" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P58" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q58" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="R58" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S58" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T58" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -4663,55 +4579,52 @@
         <v>76</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C59" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D59" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E59" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F59" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G59" s="2">
         <v>45883</v>
       </c>
       <c r="H59" t="s">
-        <v>295</v>
-      </c>
-      <c r="I59" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="L59" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M59" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N59" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O59" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P59" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q59" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="R59" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="S59" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="T59" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="60" spans="1:20">
@@ -4719,55 +4632,58 @@
         <v>77</v>
       </c>
       <c r="B60" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D60" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E60" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F60" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G60" s="2">
         <v>45884</v>
       </c>
       <c r="H60" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I60" t="s">
         <v>312</v>
       </c>
+      <c r="J60" t="s">
+        <v>318</v>
+      </c>
       <c r="L60" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M60" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N60" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O60" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P60" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q60" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R60" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="S60" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="T60" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -4775,55 +4691,55 @@
         <v>78</v>
       </c>
       <c r="B61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C61" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D61" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E61" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F61" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G61" s="2">
         <v>45885</v>
       </c>
       <c r="H61" t="s">
-        <v>296</v>
-      </c>
-      <c r="I61" t="s">
-        <v>312</v>
+        <v>293</v>
+      </c>
+      <c r="J61" t="s">
+        <v>319</v>
       </c>
       <c r="L61" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M61" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N61" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O61" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P61" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q61" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="R61" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="S61" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="T61" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="62" spans="1:20">
@@ -4831,55 +4747,58 @@
         <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C62" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D62" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E62" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F62" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G62" s="2">
         <v>45886</v>
       </c>
       <c r="H62" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I62" t="s">
-        <v>312</v>
+        <v>313</v>
+      </c>
+      <c r="J62" t="s">
+        <v>317</v>
       </c>
       <c r="L62" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M62" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N62" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O62" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P62" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q62" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="R62" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="S62" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="T62" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="63" spans="1:20">
@@ -4887,55 +4806,52 @@
         <v>80</v>
       </c>
       <c r="B63" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C63" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D63" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E63" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F63" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G63" s="2">
         <v>45887</v>
       </c>
       <c r="H63" t="s">
-        <v>298</v>
-      </c>
-      <c r="I63" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="L63" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M63" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N63" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O63" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P63" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q63" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="R63" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="S63" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="T63" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
     </row>
     <row r="64" spans="1:20">
@@ -4943,55 +4859,58 @@
         <v>81</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C64" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D64" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E64" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F64" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G64" s="2">
         <v>45888</v>
       </c>
       <c r="H64" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I64" t="s">
-        <v>312</v>
+        <v>314</v>
+      </c>
+      <c r="J64" t="s">
+        <v>318</v>
       </c>
       <c r="L64" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M64" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N64" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O64" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P64" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q64" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R64" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S64" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T64" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="65" spans="1:20">
@@ -4999,55 +4918,55 @@
         <v>82</v>
       </c>
       <c r="B65" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D65" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E65" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F65" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G65" s="2">
         <v>45889</v>
       </c>
       <c r="H65" t="s">
-        <v>300</v>
-      </c>
-      <c r="I65" t="s">
-        <v>312</v>
+        <v>297</v>
+      </c>
+      <c r="J65" t="s">
+        <v>317</v>
       </c>
       <c r="L65" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M65" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N65" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O65" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P65" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q65" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="R65" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="S65" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="T65" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -5055,58 +4974,55 @@
         <v>83</v>
       </c>
       <c r="B66" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C66" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D66" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E66" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F66" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G66" s="2">
         <v>45877</v>
       </c>
       <c r="H66" t="s">
-        <v>258</v>
-      </c>
-      <c r="I66" t="s">
-        <v>311</v>
-      </c>
-      <c r="K66" t="s">
-        <v>313</v>
+        <v>255</v>
+      </c>
+      <c r="J66" t="s">
+        <v>318</v>
       </c>
       <c r="L66" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M66" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N66" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O66" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P66" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q66" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R66" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S66" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T66" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="67" spans="1:20">
@@ -5114,58 +5030,55 @@
         <v>83</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C67" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D67" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E67" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F67" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G67" s="2">
         <v>45877</v>
       </c>
       <c r="H67" t="s">
-        <v>255</v>
-      </c>
-      <c r="I67" t="s">
-        <v>311</v>
+        <v>252</v>
       </c>
       <c r="K67" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L67" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M67" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N67" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O67" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P67" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q67" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R67" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="S67" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="T67" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -5173,58 +5086,55 @@
         <v>84</v>
       </c>
       <c r="B68" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C68" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D68" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E68" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F68" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G68" s="2">
-        <v>45880</v>
+        <v>45879</v>
       </c>
       <c r="H68" t="s">
-        <v>258</v>
-      </c>
-      <c r="I68" t="s">
-        <v>311</v>
-      </c>
-      <c r="K68" t="s">
-        <v>313</v>
+        <v>298</v>
+      </c>
+      <c r="J68" t="s">
+        <v>317</v>
       </c>
       <c r="L68" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M68" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N68" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O68" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P68" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q68" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R68" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="S68" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="T68" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="1:20">
@@ -5232,58 +5142,55 @@
         <v>84</v>
       </c>
       <c r="B69" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C69" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D69" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E69" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F69" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G69" s="2">
-        <v>45880</v>
+        <v>45879</v>
       </c>
       <c r="H69" t="s">
-        <v>255</v>
-      </c>
-      <c r="I69" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="K69" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="L69" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M69" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N69" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O69" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P69" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q69" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R69" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="S69" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="T69" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
     </row>
     <row r="70" spans="1:20">
@@ -5291,58 +5198,55 @@
         <v>85</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C70" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D70" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E70" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F70" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G70" s="2">
-        <v>45883</v>
+        <v>45881</v>
       </c>
       <c r="H70" t="s">
-        <v>258</v>
-      </c>
-      <c r="I70" t="s">
-        <v>311</v>
-      </c>
-      <c r="K70" t="s">
-        <v>313</v>
+        <v>300</v>
+      </c>
+      <c r="J70" t="s">
+        <v>319</v>
       </c>
       <c r="L70" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M70" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N70" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O70" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P70" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q70" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R70" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="S70" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="T70" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="71" spans="1:20">
@@ -5350,58 +5254,55 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C71" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D71" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E71" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F71" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G71" s="2">
-        <v>45883</v>
+        <v>45881</v>
       </c>
       <c r="H71" t="s">
-        <v>255</v>
-      </c>
-      <c r="I71" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="K71" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="L71" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M71" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N71" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O71" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P71" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q71" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R71" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="S71" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="T71" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:20">
@@ -5409,58 +5310,55 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C72" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E72" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F72" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G72" s="2">
-        <v>45872</v>
+        <v>45883</v>
       </c>
       <c r="H72" t="s">
-        <v>258</v>
-      </c>
-      <c r="I72" t="s">
-        <v>311</v>
-      </c>
-      <c r="K72" t="s">
-        <v>313</v>
+        <v>255</v>
+      </c>
+      <c r="J72" t="s">
+        <v>318</v>
       </c>
       <c r="L72" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M72" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N72" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O72" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P72" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q72" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R72" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="S72" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="T72" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
     <row r="73" spans="1:20">
@@ -5468,58 +5366,55 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C73" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D73" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E73" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F73" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G73" s="2">
-        <v>45872</v>
+        <v>45883</v>
       </c>
       <c r="H73" t="s">
-        <v>255</v>
-      </c>
-      <c r="I73" t="s">
-        <v>311</v>
+        <v>252</v>
       </c>
       <c r="K73" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="L73" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M73" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N73" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O73" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P73" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q73" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R73" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="S73" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="T73" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -5527,341 +5422,335 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C74" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D74" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E74" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F74" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G74" s="2">
-        <v>45875</v>
+        <v>45886</v>
       </c>
       <c r="H74" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="I74" t="s">
-        <v>311</v>
-      </c>
-      <c r="K74" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L74" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M74" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N74" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O74" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P74" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q74" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R74" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="S74" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="T74" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B75" t="s">
         <v>163</v>
       </c>
       <c r="C75" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D75" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E75" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F75" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G75" s="2">
-        <v>45875</v>
+        <v>45889</v>
       </c>
       <c r="H75" t="s">
-        <v>255</v>
+        <v>303</v>
       </c>
       <c r="I75" t="s">
-        <v>311</v>
-      </c>
-      <c r="K75" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L75" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M75" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N75" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O75" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P75" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q75" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R75" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="S75" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="T75" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B76" t="s">
         <v>164</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D76" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E76" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F76" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G76" s="2">
-        <v>45886</v>
+        <v>45870</v>
       </c>
       <c r="H76" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I76" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L76" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M76" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N76" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O76" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P76" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q76" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R76" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="S76" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="T76" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B77" t="s">
         <v>165</v>
       </c>
       <c r="C77" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E77" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F77" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G77" s="2">
-        <v>45889</v>
+        <v>45873</v>
       </c>
       <c r="H77" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I77" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L77" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M77" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N77" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O77" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P77" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q77" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R77" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="S77" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="T77" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B78" t="s">
         <v>166</v>
       </c>
       <c r="C78" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E78" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F78" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G78" s="2">
-        <v>45870</v>
+        <v>45876</v>
       </c>
       <c r="H78" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="I78" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L78" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M78" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N78" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O78" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P78" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q78" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R78" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="S78" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="T78" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B79" t="s">
         <v>167</v>
       </c>
       <c r="C79" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D79" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E79" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F79" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G79" s="2">
-        <v>45873</v>
+        <v>45880</v>
       </c>
       <c r="H79" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I79" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="L79" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M79" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N79" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O79" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P79" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q79" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R79" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="S79" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="T79" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:20">
@@ -5869,55 +5758,55 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D80" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E80" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F80" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G80" s="2">
-        <v>45876</v>
+        <v>45880</v>
       </c>
       <c r="H80" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I80" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L80" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M80" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N80" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O80" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P80" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q80" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R80" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="S80" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="T80" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:20">
@@ -5925,55 +5814,55 @@
         <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C81" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D81" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E81" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F81" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G81" s="2">
-        <v>45880</v>
+        <v>45882</v>
       </c>
       <c r="H81" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I81" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="L81" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M81" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N81" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O81" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P81" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q81" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R81" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="S81" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="T81" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:20">
@@ -5981,55 +5870,55 @@
         <v>93</v>
       </c>
       <c r="B82" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C82" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D82" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E82" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F82" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G82" s="2">
-        <v>45880</v>
+        <v>45882</v>
       </c>
       <c r="H82" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I82" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L82" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M82" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N82" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O82" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P82" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q82" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R82" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="S82" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="T82" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:20">
@@ -6037,55 +5926,55 @@
         <v>94</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C83" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D83" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E83" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F83" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G83" s="2">
-        <v>45882</v>
+        <v>45885</v>
       </c>
       <c r="H83" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I83" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="L83" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M83" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N83" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O83" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P83" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q83" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R83" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S83" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="T83" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -6093,167 +5982,55 @@
         <v>94</v>
       </c>
       <c r="B84" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C84" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E84" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F84" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G84" s="2">
-        <v>45882</v>
+        <v>45885</v>
       </c>
       <c r="H84" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I84" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="L84" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="M84" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N84" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="O84" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P84" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="Q84" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="R84" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="S84" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="T84" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20">
-      <c r="A85" t="s">
-        <v>95</v>
-      </c>
-      <c r="B85" t="s">
-        <v>171</v>
-      </c>
-      <c r="C85" t="s">
-        <v>172</v>
-      </c>
-      <c r="D85" t="s">
-        <v>173</v>
-      </c>
-      <c r="E85" t="s">
-        <v>249</v>
-      </c>
-      <c r="F85" t="s">
-        <v>250</v>
-      </c>
-      <c r="G85" s="2">
-        <v>45885</v>
-      </c>
-      <c r="H85" t="s">
-        <v>308</v>
-      </c>
-      <c r="I85" t="s">
-        <v>309</v>
-      </c>
-      <c r="L85" t="s">
-        <v>314</v>
-      </c>
-      <c r="M85" t="s">
-        <v>315</v>
-      </c>
-      <c r="N85" t="s">
-        <v>316</v>
-      </c>
-      <c r="O85" t="s">
-        <v>317</v>
-      </c>
-      <c r="P85" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>319</v>
-      </c>
-      <c r="R85" t="s">
-        <v>323</v>
-      </c>
-      <c r="S85" t="s">
-        <v>332</v>
-      </c>
-      <c r="T85" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20">
-      <c r="A86" t="s">
-        <v>95</v>
-      </c>
-      <c r="B86" t="s">
-        <v>171</v>
-      </c>
-      <c r="C86" t="s">
-        <v>172</v>
-      </c>
-      <c r="D86" t="s">
-        <v>173</v>
-      </c>
-      <c r="E86" t="s">
-        <v>249</v>
-      </c>
-      <c r="F86" t="s">
-        <v>250</v>
-      </c>
-      <c r="G86" s="2">
-        <v>45885</v>
-      </c>
-      <c r="H86" t="s">
-        <v>308</v>
-      </c>
-      <c r="I86" t="s">
-        <v>309</v>
-      </c>
-      <c r="L86" t="s">
-        <v>314</v>
-      </c>
-      <c r="M86" t="s">
-        <v>315</v>
-      </c>
-      <c r="N86" t="s">
-        <v>316</v>
-      </c>
-      <c r="O86" t="s">
-        <v>317</v>
-      </c>
-      <c r="P86" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>319</v>
-      </c>
-      <c r="R86" t="s">
-        <v>331</v>
-      </c>
-      <c r="S86" t="s">
-        <v>337</v>
-      </c>
-      <c r="T86" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="417">
   <si>
     <t>Código Produto</t>
   </si>
@@ -37,6 +37,9 @@
     <t>Data Aceite</t>
   </si>
   <si>
+    <t>Valor Orçado</t>
+  </si>
+  <si>
     <t>Valor Realizado</t>
   </si>
   <si>
@@ -763,184 +766,379 @@
     <t>PENDENTE</t>
   </si>
   <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>72000</t>
-  </si>
-  <si>
-    <t>48000</t>
-  </si>
-  <si>
-    <t>120000</t>
+    <t>16500</t>
+  </si>
+  <si>
+    <t>19800</t>
+  </si>
+  <si>
+    <t>14300</t>
+  </si>
+  <si>
+    <t>9900</t>
+  </si>
+  <si>
+    <t>115500</t>
+  </si>
+  <si>
+    <t>6600.000000000001</t>
+  </si>
+  <si>
+    <t>15400</t>
+  </si>
+  <si>
+    <t>17600</t>
+  </si>
+  <si>
+    <t>22000</t>
+  </si>
+  <si>
+    <t>24200</t>
+  </si>
+  <si>
+    <t>26400</t>
+  </si>
+  <si>
+    <t>5500</t>
+  </si>
+  <si>
+    <t>5830.000000000001</t>
+  </si>
+  <si>
+    <t>6160.000000000001</t>
+  </si>
+  <si>
+    <t>6490.000000000001</t>
+  </si>
+  <si>
+    <t>6820.000000000001</t>
+  </si>
+  <si>
+    <t>7150.000000000001</t>
+  </si>
+  <si>
+    <t>7480.000000000001</t>
+  </si>
+  <si>
+    <t>9460</t>
+  </si>
+  <si>
+    <t>9790</t>
+  </si>
+  <si>
+    <t>10450</t>
+  </si>
+  <si>
+    <t>10780</t>
+  </si>
+  <si>
+    <t>11440</t>
+  </si>
+  <si>
+    <t>11770</t>
+  </si>
+  <si>
+    <t>12100</t>
+  </si>
+  <si>
+    <t>12430</t>
+  </si>
+  <si>
+    <t>12760</t>
+  </si>
+  <si>
+    <t>13090</t>
+  </si>
+  <si>
+    <t>13420</t>
+  </si>
+  <si>
+    <t>13750</t>
+  </si>
+  <si>
+    <t>14080</t>
+  </si>
+  <si>
+    <t>16390</t>
+  </si>
+  <si>
+    <t>16720</t>
+  </si>
+  <si>
+    <t>17380</t>
+  </si>
+  <si>
+    <t>17710</t>
+  </si>
+  <si>
+    <t>30800</t>
+  </si>
+  <si>
+    <t>35200</t>
+  </si>
+  <si>
+    <t>16940</t>
+  </si>
+  <si>
+    <t>17820</t>
+  </si>
+  <si>
+    <t>18260</t>
+  </si>
+  <si>
+    <t>18700</t>
+  </si>
+  <si>
+    <t>19140</t>
+  </si>
+  <si>
+    <t>19580</t>
+  </si>
+  <si>
+    <t>20020</t>
+  </si>
+  <si>
+    <t>20460</t>
+  </si>
+  <si>
+    <t>20900</t>
+  </si>
+  <si>
+    <t>21340</t>
+  </si>
+  <si>
+    <t>21780</t>
+  </si>
+  <si>
+    <t>22220</t>
+  </si>
+  <si>
+    <t>22660</t>
+  </si>
+  <si>
+    <t>23100</t>
+  </si>
+  <si>
+    <t>23540</t>
+  </si>
+  <si>
+    <t>23980</t>
+  </si>
+  <si>
+    <t>24420</t>
+  </si>
+  <si>
+    <t>24860</t>
+  </si>
+  <si>
+    <t>13200</t>
+  </si>
+  <si>
+    <t>55000.00000000001</t>
+  </si>
+  <si>
+    <t>49500.00000000001</t>
+  </si>
+  <si>
+    <t>60500.00000000001</t>
+  </si>
+  <si>
+    <t>41800</t>
+  </si>
+  <si>
+    <t>46200.00000000001</t>
+  </si>
+  <si>
+    <t>38500</t>
+  </si>
+  <si>
+    <t>44000</t>
+  </si>
+  <si>
+    <t>41250</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>13000</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>16000</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>5300</t>
+  </si>
+  <si>
+    <t>5600</t>
+  </si>
+  <si>
+    <t>5900</t>
+  </si>
+  <si>
+    <t>6200</t>
+  </si>
+  <si>
+    <t>6500</t>
+  </si>
+  <si>
+    <t>6800</t>
+  </si>
+  <si>
+    <t>8600</t>
+  </si>
+  <si>
+    <t>8900</t>
+  </si>
+  <si>
+    <t>9500</t>
+  </si>
+  <si>
+    <t>9800</t>
+  </si>
+  <si>
+    <t>10400</t>
+  </si>
+  <si>
+    <t>10700</t>
+  </si>
+  <si>
+    <t>11000</t>
+  </si>
+  <si>
+    <t>11300</t>
+  </si>
+  <si>
+    <t>11600</t>
+  </si>
+  <si>
+    <t>11900</t>
+  </si>
+  <si>
+    <t>12200</t>
+  </si>
+  <si>
+    <t>12500</t>
+  </si>
+  <si>
+    <t>12800</t>
+  </si>
+  <si>
+    <t>14900</t>
+  </si>
+  <si>
+    <t>15200</t>
+  </si>
+  <si>
+    <t>15800</t>
+  </si>
+  <si>
+    <t>16100</t>
+  </si>
+  <si>
+    <t>28000</t>
   </si>
   <si>
     <t>32000</t>
   </si>
   <si>
-    <t>65000</t>
-  </si>
-  <si>
-    <t>70000</t>
-  </si>
-  <si>
-    <t>75000</t>
-  </si>
-  <si>
-    <t>85000</t>
-  </si>
-  <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>110000</t>
-  </si>
-  <si>
-    <t>130000</t>
+    <t>16200</t>
+  </si>
+  <si>
+    <t>16600</t>
+  </si>
+  <si>
+    <t>17000</t>
+  </si>
+  <si>
+    <t>17400</t>
+  </si>
+  <si>
+    <t>17800</t>
+  </si>
+  <si>
+    <t>18200</t>
+  </si>
+  <si>
+    <t>18600</t>
+  </si>
+  <si>
+    <t>19000</t>
+  </si>
+  <si>
+    <t>19400</t>
+  </si>
+  <si>
+    <t>20200</t>
+  </si>
+  <si>
+    <t>20600</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>21400</t>
+  </si>
+  <si>
+    <t>21800</t>
+  </si>
+  <si>
+    <t>22200</t>
+  </si>
+  <si>
+    <t>22600</t>
+  </si>
+  <si>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
+    <t>55000</t>
   </si>
   <si>
     <t>38000</t>
   </si>
   <si>
-    <t>39000</t>
+    <t>42000</t>
+  </si>
+  <si>
+    <t>35000</t>
   </si>
   <si>
     <t>40000</t>
   </si>
   <si>
-    <t>41000</t>
-  </si>
-  <si>
-    <t>42000</t>
-  </si>
-  <si>
-    <t>43000</t>
-  </si>
-  <si>
-    <t>44000</t>
-  </si>
-  <si>
-    <t>50000</t>
-  </si>
-  <si>
-    <t>51000</t>
-  </si>
-  <si>
-    <t>53000</t>
-  </si>
-  <si>
-    <t>54000</t>
-  </si>
-  <si>
-    <t>56000</t>
-  </si>
-  <si>
-    <t>57000</t>
-  </si>
-  <si>
-    <t>58000</t>
-  </si>
-  <si>
-    <t>59000</t>
-  </si>
-  <si>
-    <t>60000</t>
-  </si>
-  <si>
-    <t>61000</t>
-  </si>
-  <si>
-    <t>62000</t>
-  </si>
-  <si>
-    <t>63000</t>
-  </si>
-  <si>
-    <t>64000</t>
-  </si>
-  <si>
-    <t>71000</t>
-  </si>
-  <si>
-    <t>74000</t>
-  </si>
-  <si>
-    <t>28000</t>
-  </si>
-  <si>
-    <t>30500</t>
-  </si>
-  <si>
-    <t>31000</t>
-  </si>
-  <si>
-    <t>31500</t>
-  </si>
-  <si>
-    <t>32500</t>
-  </si>
-  <si>
-    <t>33000</t>
-  </si>
-  <si>
-    <t>33500</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>34500</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>35500</t>
-  </si>
-  <si>
-    <t>36000</t>
-  </si>
-  <si>
-    <t>36500</t>
-  </si>
-  <si>
-    <t>37000</t>
-  </si>
-  <si>
     <t>37500</t>
-  </si>
-  <si>
-    <t>38500</t>
-  </si>
-  <si>
-    <t>39500</t>
-  </si>
-  <si>
-    <t>15000</t>
-  </si>
-  <si>
-    <t>12000</t>
-  </si>
-  <si>
-    <t>14000</t>
-  </si>
-  <si>
-    <t>11000</t>
-  </si>
-  <si>
-    <t>16000</t>
-  </si>
-  <si>
-    <t>13000</t>
-  </si>
-  <si>
-    <t>45000</t>
-  </si>
-  <si>
-    <t>55000</t>
   </si>
   <si>
     <t>ROSANA.MARTINS</t>
@@ -1428,10 +1626,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T84"/>
+  <dimension ref="A1:U84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1492,2444 +1690,2570 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G2" s="2">
         <v>45870</v>
       </c>
       <c r="H2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="J2" t="s">
-        <v>316</v>
-      </c>
-      <c r="L2" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K2" t="s">
+        <v>382</v>
       </c>
       <c r="M2" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N2" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O2" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P2" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q2" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R2" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S2" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G3" s="2">
         <v>45875</v>
       </c>
       <c r="H3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="J3" t="s">
-        <v>316</v>
-      </c>
-      <c r="L3" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K3" t="s">
+        <v>382</v>
       </c>
       <c r="M3" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N3" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O3" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P3" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q3" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R3" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S3" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G4" s="2">
         <v>45880</v>
       </c>
       <c r="H4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I4" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="J4" t="s">
-        <v>316</v>
-      </c>
-      <c r="L4" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K4" t="s">
+        <v>382</v>
       </c>
       <c r="M4" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N4" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O4" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P4" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q4" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R4" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S4" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T4" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G5" s="2">
         <v>45880</v>
       </c>
       <c r="H5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I5" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="J5" t="s">
-        <v>316</v>
-      </c>
-      <c r="L5" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K5" t="s">
+        <v>382</v>
       </c>
       <c r="M5" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N5" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O5" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P5" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q5" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R5" t="s">
-        <v>329</v>
+        <v>390</v>
       </c>
       <c r="S5" t="s">
-        <v>341</v>
+        <v>395</v>
       </c>
       <c r="T5" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
+        <v>407</v>
+      </c>
+      <c r="U5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G6" s="2">
         <v>45885</v>
       </c>
       <c r="H6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I6" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="J6" t="s">
-        <v>316</v>
-      </c>
-      <c r="L6" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K6" t="s">
+        <v>382</v>
       </c>
       <c r="M6" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N6" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O6" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P6" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q6" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="R6" t="s">
-        <v>330</v>
+        <v>391</v>
       </c>
       <c r="S6" t="s">
-        <v>342</v>
+        <v>396</v>
       </c>
       <c r="T6" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20">
+        <v>408</v>
+      </c>
+      <c r="U6" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G7" s="2">
         <v>45872</v>
       </c>
       <c r="H7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I7" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="J7" t="s">
-        <v>316</v>
-      </c>
-      <c r="L7" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K7" t="s">
+        <v>382</v>
       </c>
       <c r="M7" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N7" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O7" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P7" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q7" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R7" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S7" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U7" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G8" s="2">
         <v>45888</v>
       </c>
       <c r="H8" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="I8" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="J8" t="s">
-        <v>316</v>
-      </c>
-      <c r="L8" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K8" t="s">
+        <v>382</v>
       </c>
       <c r="M8" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N8" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O8" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P8" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q8" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R8" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S8" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G9" s="2">
         <v>45871</v>
       </c>
       <c r="H9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I9" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="J9" t="s">
-        <v>316</v>
-      </c>
-      <c r="L9" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K9" t="s">
+        <v>382</v>
       </c>
       <c r="M9" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N9" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O9" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P9" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q9" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R9" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S9" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U9" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G10" s="2">
         <v>45872</v>
       </c>
       <c r="H10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I10" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="J10" t="s">
-        <v>316</v>
-      </c>
-      <c r="L10" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K10" t="s">
+        <v>382</v>
       </c>
       <c r="M10" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N10" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O10" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P10" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q10" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R10" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S10" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T10" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U10" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G11" s="2">
         <v>45873</v>
       </c>
       <c r="H11" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="I11" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="J11" t="s">
-        <v>316</v>
-      </c>
-      <c r="L11" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K11" t="s">
+        <v>382</v>
       </c>
       <c r="M11" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N11" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O11" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P11" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q11" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R11" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S11" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T11" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G12" s="2">
         <v>45874</v>
       </c>
       <c r="H12" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="I12" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="J12" t="s">
-        <v>316</v>
-      </c>
-      <c r="L12" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K12" t="s">
+        <v>382</v>
       </c>
       <c r="M12" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N12" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O12" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P12" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q12" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R12" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S12" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T12" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U12" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G13" s="2">
         <v>45875</v>
       </c>
       <c r="H13" t="s">
+        <v>259</v>
+      </c>
+      <c r="I13" t="s">
         <v>258</v>
       </c>
-      <c r="I13" t="s">
-        <v>309</v>
-      </c>
       <c r="J13" t="s">
-        <v>316</v>
-      </c>
-      <c r="L13" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K13" t="s">
+        <v>382</v>
       </c>
       <c r="M13" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N13" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O13" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P13" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q13" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R13" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S13" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T13" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U13" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G14" s="2">
         <v>45876</v>
       </c>
       <c r="H14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I14" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="J14" t="s">
-        <v>316</v>
-      </c>
-      <c r="L14" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K14" t="s">
+        <v>382</v>
       </c>
       <c r="M14" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N14" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O14" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P14" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q14" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R14" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S14" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T14" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U14" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G15" s="2">
         <v>45872</v>
       </c>
       <c r="H15" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="I15" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="J15" t="s">
-        <v>317</v>
-      </c>
-      <c r="L15" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K15" t="s">
+        <v>383</v>
       </c>
       <c r="M15" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N15" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O15" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P15" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q15" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R15" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="S15" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T15" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U15" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G16" s="2">
         <v>45873</v>
       </c>
       <c r="H16" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I16" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="J16" t="s">
-        <v>317</v>
-      </c>
-      <c r="L16" t="s">
-        <v>319</v>
+        <v>379</v>
+      </c>
+      <c r="K16" t="s">
+        <v>383</v>
       </c>
       <c r="M16" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N16" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O16" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P16" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q16" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R16" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="S16" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T16" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U16" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G17" s="2">
         <v>45874</v>
       </c>
       <c r="H17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I17" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J17" t="s">
-        <v>317</v>
-      </c>
-      <c r="L17" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K17" t="s">
+        <v>383</v>
       </c>
       <c r="M17" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N17" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O17" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P17" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q17" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R17" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="S17" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T17" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U17" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G18" s="2">
         <v>45875</v>
       </c>
       <c r="H18" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I18" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="J18" t="s">
-        <v>317</v>
-      </c>
-      <c r="L18" t="s">
-        <v>319</v>
+        <v>379</v>
+      </c>
+      <c r="K18" t="s">
+        <v>383</v>
       </c>
       <c r="M18" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N18" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O18" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P18" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q18" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R18" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="S18" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T18" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U18" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F19" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G19" s="2">
         <v>45876</v>
       </c>
       <c r="H19" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="I19" t="s">
-        <v>312</v>
+        <v>258</v>
       </c>
       <c r="J19" t="s">
-        <v>317</v>
-      </c>
-      <c r="L19" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K19" t="s">
+        <v>383</v>
       </c>
       <c r="M19" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N19" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O19" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P19" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q19" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R19" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="S19" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T19" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U19" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G20" s="2">
         <v>45877</v>
       </c>
       <c r="H20" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="I20" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="J20" t="s">
-        <v>317</v>
-      </c>
-      <c r="L20" t="s">
-        <v>319</v>
+        <v>379</v>
+      </c>
+      <c r="K20" t="s">
+        <v>383</v>
       </c>
       <c r="M20" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N20" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O20" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P20" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q20" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R20" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="S20" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T20" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U20" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G21" s="2">
         <v>45878</v>
       </c>
       <c r="H21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I21" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="J21" t="s">
-        <v>316</v>
-      </c>
-      <c r="L21" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K21" t="s">
+        <v>382</v>
       </c>
       <c r="M21" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N21" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O21" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P21" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q21" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R21" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S21" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T21" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U21" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G22" s="2">
         <v>45879</v>
       </c>
       <c r="H22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I22" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="J22" t="s">
-        <v>316</v>
-      </c>
-      <c r="L22" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K22" t="s">
+        <v>382</v>
       </c>
       <c r="M22" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N22" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O22" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P22" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q22" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R22" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S22" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T22" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U22" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G23" s="2">
         <v>45874</v>
       </c>
       <c r="H23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I23" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="J23" t="s">
-        <v>316</v>
-      </c>
-      <c r="L23" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K23" t="s">
+        <v>382</v>
       </c>
       <c r="M23" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N23" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O23" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P23" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q23" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R23" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S23" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T23" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U23" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F24" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G24" s="2">
         <v>45881</v>
       </c>
       <c r="H24" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I24" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="J24" t="s">
-        <v>316</v>
-      </c>
-      <c r="L24" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K24" t="s">
+        <v>382</v>
       </c>
       <c r="M24" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N24" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O24" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P24" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q24" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R24" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S24" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T24" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U24" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F25" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G25" s="2">
         <v>45882</v>
       </c>
       <c r="H25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I25" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="J25" t="s">
-        <v>316</v>
-      </c>
-      <c r="L25" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K25" t="s">
+        <v>382</v>
       </c>
       <c r="M25" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N25" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O25" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P25" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q25" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R25" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S25" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T25" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U25" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G26" s="2">
         <v>45877</v>
       </c>
       <c r="H26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I26" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="J26" t="s">
-        <v>316</v>
-      </c>
-      <c r="L26" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K26" t="s">
+        <v>382</v>
       </c>
       <c r="M26" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N26" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O26" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P26" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q26" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R26" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S26" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T26" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U26" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D27" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E27" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F27" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G27" s="2">
         <v>45884</v>
       </c>
       <c r="H27" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I27" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="J27" t="s">
-        <v>316</v>
-      </c>
-      <c r="L27" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K27" t="s">
+        <v>382</v>
       </c>
       <c r="M27" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N27" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O27" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P27" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q27" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R27" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S27" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T27" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U27" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E28" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F28" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G28" s="2">
         <v>45870</v>
       </c>
       <c r="H28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I28" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="J28" t="s">
-        <v>316</v>
-      </c>
-      <c r="L28" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K28" t="s">
+        <v>382</v>
       </c>
       <c r="M28" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N28" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O28" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P28" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q28" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R28" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S28" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T28" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U28" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D29" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F29" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G29" s="2">
         <v>45871</v>
       </c>
       <c r="H29" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I29" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="J29" t="s">
-        <v>316</v>
-      </c>
-      <c r="L29" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K29" t="s">
+        <v>382</v>
       </c>
       <c r="M29" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N29" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O29" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P29" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q29" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R29" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S29" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T29" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U29" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E30" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F30" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G30" s="2">
         <v>45873</v>
       </c>
       <c r="H30" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I30" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="J30" t="s">
-        <v>316</v>
-      </c>
-      <c r="L30" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K30" t="s">
+        <v>382</v>
       </c>
       <c r="M30" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N30" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O30" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P30" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q30" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R30" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S30" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T30" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U30" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E31" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F31" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G31" s="2">
         <v>45874</v>
       </c>
       <c r="H31" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I31" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="J31" t="s">
-        <v>316</v>
-      </c>
-      <c r="L31" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K31" t="s">
+        <v>382</v>
       </c>
       <c r="M31" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N31" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O31" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P31" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q31" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R31" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S31" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T31" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U31" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E32" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G32" s="2">
         <v>45876</v>
       </c>
       <c r="H32" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I32" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="J32" t="s">
-        <v>316</v>
-      </c>
-      <c r="L32" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K32" t="s">
+        <v>382</v>
       </c>
       <c r="M32" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N32" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O32" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P32" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q32" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R32" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S32" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T32" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U32" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F33" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G33" s="2">
         <v>45877</v>
       </c>
       <c r="H33" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I33" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="J33" t="s">
-        <v>316</v>
-      </c>
-      <c r="L33" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K33" t="s">
+        <v>382</v>
       </c>
       <c r="M33" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N33" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O33" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P33" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q33" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R33" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S33" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T33" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U33" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D34" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F34" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G34" s="2">
         <v>45872</v>
       </c>
       <c r="H34" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I34" t="s">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="J34" t="s">
-        <v>316</v>
-      </c>
-      <c r="L34" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K34" t="s">
+        <v>382</v>
       </c>
       <c r="M34" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N34" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O34" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P34" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q34" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R34" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S34" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T34" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U34" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F35" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G35" s="2">
         <v>45879</v>
       </c>
       <c r="H35" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I35" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="J35" t="s">
-        <v>316</v>
-      </c>
-      <c r="L35" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K35" t="s">
+        <v>382</v>
       </c>
       <c r="M35" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N35" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O35" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P35" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q35" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R35" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S35" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T35" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U35" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E36" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F36" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G36" s="2">
         <v>45880</v>
       </c>
       <c r="H36" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I36" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="J36" t="s">
-        <v>316</v>
-      </c>
-      <c r="L36" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K36" t="s">
+        <v>382</v>
       </c>
       <c r="M36" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N36" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O36" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P36" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q36" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R36" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S36" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T36" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U36" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F37" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G37" s="2">
         <v>45875</v>
       </c>
       <c r="H37" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I37" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="J37" t="s">
-        <v>316</v>
-      </c>
-      <c r="L37" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K37" t="s">
+        <v>382</v>
       </c>
       <c r="M37" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N37" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O37" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P37" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q37" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R37" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S37" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T37" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U37" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G38" s="2">
         <v>45882</v>
       </c>
       <c r="H38" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I38" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="J38" t="s">
-        <v>316</v>
-      </c>
-      <c r="L38" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K38" t="s">
+        <v>382</v>
       </c>
       <c r="M38" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N38" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O38" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P38" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q38" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R38" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S38" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T38" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U38" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E39" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F39" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G39" s="2">
         <v>45883</v>
       </c>
       <c r="H39" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I39" t="s">
-        <v>309</v>
+        <v>342</v>
       </c>
       <c r="J39" t="s">
-        <v>316</v>
-      </c>
-      <c r="L39" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K39" t="s">
+        <v>382</v>
       </c>
       <c r="M39" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N39" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O39" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P39" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q39" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R39" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S39" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T39" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U39" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D40" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E40" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F40" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G40" s="2">
         <v>45878</v>
       </c>
       <c r="H40" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I40" t="s">
-        <v>310</v>
+        <v>343</v>
       </c>
       <c r="J40" t="s">
-        <v>316</v>
-      </c>
-      <c r="L40" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K40" t="s">
+        <v>382</v>
       </c>
       <c r="M40" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N40" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O40" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P40" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q40" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R40" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S40" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T40" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U40" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G41" s="2">
         <v>45871</v>
       </c>
       <c r="H41" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I41" t="s">
-        <v>311</v>
+        <v>344</v>
       </c>
       <c r="J41" t="s">
-        <v>316</v>
-      </c>
-      <c r="L41" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K41" t="s">
+        <v>382</v>
       </c>
       <c r="M41" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N41" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O41" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P41" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q41" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R41" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S41" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T41" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U41" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F42" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G42" s="2">
         <v>45872</v>
       </c>
       <c r="H42" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="I42" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="J42" t="s">
-        <v>316</v>
-      </c>
-      <c r="L42" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K42" t="s">
+        <v>382</v>
       </c>
       <c r="M42" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N42" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O42" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P42" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q42" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R42" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S42" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T42" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U42" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F43" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G43" s="2">
         <v>45874</v>
@@ -3938,1886 +4262,1982 @@
         <v>283</v>
       </c>
       <c r="I43" t="s">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="J43" t="s">
-        <v>316</v>
-      </c>
-      <c r="L43" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K43" t="s">
+        <v>382</v>
       </c>
       <c r="M43" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N43" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O43" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P43" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q43" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R43" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S43" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T43" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U43" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D44" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F44" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G44" s="2">
         <v>45875</v>
       </c>
       <c r="H44" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="I44" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="J44" t="s">
-        <v>316</v>
-      </c>
-      <c r="L44" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K44" t="s">
+        <v>382</v>
       </c>
       <c r="M44" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N44" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O44" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P44" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q44" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R44" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S44" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T44" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U44" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D45" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E45" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G45" s="2">
         <v>45870</v>
       </c>
       <c r="H45" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I45" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="J45" t="s">
-        <v>317</v>
-      </c>
-      <c r="L45" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K45" t="s">
+        <v>383</v>
       </c>
       <c r="M45" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N45" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O45" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P45" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q45" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R45" t="s">
-        <v>332</v>
+        <v>390</v>
       </c>
       <c r="S45" t="s">
-        <v>341</v>
+        <v>398</v>
       </c>
       <c r="T45" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20">
+        <v>407</v>
+      </c>
+      <c r="U45" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B46" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D46" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E46" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F46" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G46" s="2">
         <v>45872</v>
       </c>
       <c r="H46" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="I46" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="J46" t="s">
-        <v>316</v>
-      </c>
-      <c r="L46" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K46" t="s">
+        <v>382</v>
       </c>
       <c r="M46" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N46" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O46" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P46" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q46" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R46" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="S46" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="T46" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20">
+        <v>410</v>
+      </c>
+      <c r="U46" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E47" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F47" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G47" s="2">
         <v>45871</v>
       </c>
       <c r="H47" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I47" t="s">
-        <v>312</v>
+        <v>256</v>
       </c>
       <c r="J47" t="s">
-        <v>317</v>
-      </c>
-      <c r="L47" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K47" t="s">
+        <v>383</v>
       </c>
       <c r="M47" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N47" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O47" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P47" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q47" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
       <c r="R47" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="S47" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="T47" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
+        <v>411</v>
+      </c>
+      <c r="U47" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D48" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E48" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F48" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G48" s="2">
         <v>45872</v>
       </c>
       <c r="H48" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I48" t="s">
-        <v>312</v>
+        <v>346</v>
       </c>
       <c r="J48" t="s">
-        <v>316</v>
-      </c>
-      <c r="L48" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K48" t="s">
+        <v>382</v>
       </c>
       <c r="M48" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N48" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O48" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P48" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q48" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R48" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="S48" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="T48" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
+        <v>410</v>
+      </c>
+      <c r="U48" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E49" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F49" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G49" s="2">
         <v>45873</v>
       </c>
       <c r="H49" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I49" t="s">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="J49" t="s">
-        <v>318</v>
-      </c>
-      <c r="L49" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K49" t="s">
+        <v>384</v>
       </c>
       <c r="M49" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N49" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O49" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P49" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q49" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="R49" t="s">
-        <v>335</v>
+        <v>393</v>
       </c>
       <c r="S49" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="T49" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20">
+        <v>412</v>
+      </c>
+      <c r="U49" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F50" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G50" s="2">
         <v>45874</v>
       </c>
       <c r="H50" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="I50" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="J50" t="s">
-        <v>317</v>
-      </c>
-      <c r="L50" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K50" t="s">
+        <v>383</v>
       </c>
       <c r="M50" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N50" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O50" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P50" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q50" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="R50" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="S50" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T50" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U50" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B51" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G51" s="2">
         <v>45875</v>
       </c>
       <c r="H51" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I51" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
       <c r="J51" t="s">
-        <v>318</v>
-      </c>
-      <c r="L51" t="s">
-        <v>319</v>
+        <v>380</v>
+      </c>
+      <c r="K51" t="s">
+        <v>384</v>
       </c>
       <c r="M51" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N51" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O51" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P51" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q51" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
       <c r="R51" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="S51" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="T51" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20">
+        <v>410</v>
+      </c>
+      <c r="U51" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E52" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G52" s="2">
         <v>45876</v>
       </c>
       <c r="H52" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I52" t="s">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="J52" t="s">
-        <v>316</v>
-      </c>
-      <c r="L52" t="s">
-        <v>319</v>
+        <v>379</v>
+      </c>
+      <c r="K52" t="s">
+        <v>382</v>
       </c>
       <c r="M52" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N52" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O52" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P52" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q52" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R52" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S52" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T52" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U52" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E53" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F53" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G53" s="2">
         <v>45877</v>
       </c>
       <c r="H53" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I53" t="s">
-        <v>312</v>
+        <v>354</v>
       </c>
       <c r="J53" t="s">
-        <v>317</v>
-      </c>
-      <c r="L53" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K53" t="s">
+        <v>383</v>
       </c>
       <c r="M53" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N53" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O53" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P53" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q53" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="R53" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="S53" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="T53" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20">
+        <v>411</v>
+      </c>
+      <c r="U53" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B54" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C54" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E54" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F54" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G54" s="2">
         <v>45878</v>
       </c>
       <c r="H54" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="I54" t="s">
-        <v>309</v>
+        <v>355</v>
       </c>
       <c r="J54" t="s">
-        <v>317</v>
-      </c>
-      <c r="L54" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K54" t="s">
+        <v>383</v>
       </c>
       <c r="M54" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N54" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O54" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P54" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q54" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="R54" t="s">
-        <v>333</v>
+        <v>391</v>
       </c>
       <c r="S54" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="T54" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20">
+        <v>410</v>
+      </c>
+      <c r="U54" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E55" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F55" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G55" s="2">
         <v>45879</v>
       </c>
       <c r="H55" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I55" t="s">
-        <v>311</v>
+        <v>356</v>
       </c>
       <c r="J55" t="s">
-        <v>316</v>
-      </c>
-      <c r="L55" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K55" t="s">
+        <v>382</v>
       </c>
       <c r="M55" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N55" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O55" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P55" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q55" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
       <c r="R55" t="s">
-        <v>335</v>
+        <v>392</v>
       </c>
       <c r="S55" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="T55" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20">
+        <v>412</v>
+      </c>
+      <c r="U55" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C56" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E56" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F56" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G56" s="2">
         <v>45880</v>
       </c>
       <c r="H56" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I56" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="J56" t="s">
-        <v>317</v>
-      </c>
-      <c r="L56" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K56" t="s">
+        <v>383</v>
       </c>
       <c r="M56" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N56" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O56" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P56" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q56" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R56" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="S56" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T56" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U56" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C57" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E57" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F57" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G57" s="2">
         <v>45881</v>
       </c>
       <c r="H57" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I57" t="s">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="J57" t="s">
-        <v>318</v>
-      </c>
-      <c r="L57" t="s">
-        <v>319</v>
+        <v>380</v>
+      </c>
+      <c r="K57" t="s">
+        <v>384</v>
       </c>
       <c r="M57" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N57" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O57" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P57" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q57" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="R57" t="s">
-        <v>333</v>
+        <v>393</v>
       </c>
       <c r="S57" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="T57" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20">
+        <v>410</v>
+      </c>
+      <c r="U57" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B58" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C58" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D58" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E58" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F58" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G58" s="2">
         <v>45882</v>
       </c>
       <c r="H58" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I58" t="s">
-        <v>312</v>
+        <v>251</v>
       </c>
       <c r="J58" t="s">
-        <v>316</v>
-      </c>
-      <c r="L58" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K58" t="s">
+        <v>382</v>
       </c>
       <c r="M58" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N58" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O58" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P58" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q58" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="R58" t="s">
-        <v>328</v>
+        <v>391</v>
       </c>
       <c r="S58" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T58" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U58" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D59" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E59" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F59" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G59" s="2">
         <v>45883</v>
       </c>
       <c r="H59" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I59" t="s">
-        <v>312</v>
+        <v>359</v>
       </c>
       <c r="J59" t="s">
-        <v>317</v>
-      </c>
-      <c r="L59" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K59" t="s">
+        <v>383</v>
       </c>
       <c r="M59" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N59" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O59" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P59" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q59" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
       <c r="R59" t="s">
-        <v>334</v>
+        <v>392</v>
       </c>
       <c r="S59" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="T59" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20">
+        <v>411</v>
+      </c>
+      <c r="U59" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D60" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E60" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F60" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G60" s="2">
         <v>45884</v>
       </c>
       <c r="H60" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I60" t="s">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="J60" t="s">
-        <v>316</v>
-      </c>
-      <c r="L60" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K60" t="s">
+        <v>382</v>
       </c>
       <c r="M60" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N60" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O60" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P60" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q60" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R60" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="S60" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="T60" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20">
+        <v>410</v>
+      </c>
+      <c r="U60" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B61" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C61" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D61" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E61" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F61" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G61" s="2">
         <v>45885</v>
       </c>
       <c r="H61" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I61" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="J61" t="s">
-        <v>318</v>
-      </c>
-      <c r="L61" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K61" t="s">
+        <v>384</v>
       </c>
       <c r="M61" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N61" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O61" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P61" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q61" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="R61" t="s">
-        <v>335</v>
+        <v>393</v>
       </c>
       <c r="S61" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="T61" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20">
+        <v>412</v>
+      </c>
+      <c r="U61" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D62" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E62" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F62" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G62" s="2">
         <v>45886</v>
       </c>
       <c r="H62" t="s">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="I62" t="s">
-        <v>313</v>
+        <v>362</v>
       </c>
       <c r="J62" t="s">
-        <v>317</v>
-      </c>
-      <c r="L62" t="s">
-        <v>319</v>
+        <v>379</v>
+      </c>
+      <c r="K62" t="s">
+        <v>383</v>
       </c>
       <c r="M62" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N62" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O62" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P62" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q62" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="R62" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="S62" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T62" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U62" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E63" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F63" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G63" s="2">
         <v>45887</v>
       </c>
       <c r="H63" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="I63" t="s">
-        <v>314</v>
+        <v>363</v>
       </c>
       <c r="J63" t="s">
-        <v>318</v>
-      </c>
-      <c r="L63" t="s">
-        <v>319</v>
+        <v>380</v>
+      </c>
+      <c r="K63" t="s">
+        <v>384</v>
       </c>
       <c r="M63" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N63" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O63" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P63" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q63" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
       <c r="R63" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
       <c r="S63" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="T63" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20">
+        <v>410</v>
+      </c>
+      <c r="U63" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B64" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E64" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G64" s="2">
         <v>45888</v>
       </c>
       <c r="H64" t="s">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="I64" t="s">
-        <v>309</v>
+        <v>364</v>
       </c>
       <c r="J64" t="s">
-        <v>316</v>
-      </c>
-      <c r="L64" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K64" t="s">
+        <v>382</v>
       </c>
       <c r="M64" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N64" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O64" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P64" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q64" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R64" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S64" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T64" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U64" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E65" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F65" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G65" s="2">
         <v>45889</v>
       </c>
       <c r="H65" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I65" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="J65" t="s">
-        <v>317</v>
-      </c>
-      <c r="L65" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K65" t="s">
+        <v>383</v>
       </c>
       <c r="M65" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N65" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O65" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P65" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q65" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="R65" t="s">
-        <v>334</v>
+        <v>393</v>
       </c>
       <c r="S65" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="T65" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20">
+        <v>411</v>
+      </c>
+      <c r="U65" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B66" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C66" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D66" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E66" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G66" s="2">
         <v>45877</v>
       </c>
       <c r="H66" t="s">
-        <v>301</v>
+        <v>250</v>
       </c>
       <c r="I66" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="J66" t="s">
-        <v>316</v>
-      </c>
-      <c r="L66" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K66" t="s">
+        <v>382</v>
       </c>
       <c r="M66" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N66" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O66" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P66" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q66" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R66" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S66" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T66" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U66" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B67" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C67" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E67" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F67" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G67" s="2">
         <v>45877</v>
       </c>
       <c r="H67" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I67" t="s">
-        <v>313</v>
-      </c>
-      <c r="K67" t="s">
-        <v>316</v>
+        <v>366</v>
+      </c>
+      <c r="J67" t="s">
+        <v>379</v>
       </c>
       <c r="L67" t="s">
-        <v>319</v>
+        <v>382</v>
       </c>
       <c r="M67" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N67" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O67" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P67" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q67" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R67" t="s">
-        <v>336</v>
+        <v>390</v>
       </c>
       <c r="S67" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="T67" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U67" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C68" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D68" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E68" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G68" s="2">
         <v>45879</v>
       </c>
       <c r="H68" t="s">
-        <v>303</v>
+        <v>256</v>
       </c>
       <c r="I68" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="J68" t="s">
-        <v>317</v>
-      </c>
-      <c r="L68" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K68" t="s">
+        <v>383</v>
       </c>
       <c r="M68" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N68" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O68" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P68" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q68" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R68" t="s">
-        <v>334</v>
+        <v>390</v>
       </c>
       <c r="S68" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="T68" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20">
+        <v>411</v>
+      </c>
+      <c r="U68" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C69" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D69" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E69" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F69" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G69" s="2">
         <v>45879</v>
       </c>
       <c r="H69" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="I69" t="s">
-        <v>310</v>
-      </c>
-      <c r="K69" t="s">
-        <v>317</v>
+        <v>337</v>
+      </c>
+      <c r="J69" t="s">
+        <v>376</v>
       </c>
       <c r="L69" t="s">
-        <v>319</v>
+        <v>383</v>
       </c>
       <c r="M69" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N69" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O69" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P69" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q69" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R69" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="S69" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="T69" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20">
+        <v>412</v>
+      </c>
+      <c r="U69" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B70" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C70" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D70" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E70" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F70" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G70" s="2">
         <v>45881</v>
       </c>
       <c r="H70" t="s">
-        <v>305</v>
+        <v>257</v>
       </c>
       <c r="I70" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J70" t="s">
-        <v>318</v>
-      </c>
-      <c r="L70" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K70" t="s">
+        <v>384</v>
       </c>
       <c r="M70" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N70" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O70" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P70" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q70" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R70" t="s">
-        <v>337</v>
+        <v>390</v>
       </c>
       <c r="S70" t="s">
-        <v>341</v>
+        <v>403</v>
       </c>
       <c r="T70" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20">
+        <v>407</v>
+      </c>
+      <c r="U70" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B71" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C71" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D71" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E71" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F71" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G71" s="2">
         <v>45881</v>
       </c>
       <c r="H71" t="s">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="I71" t="s">
-        <v>313</v>
-      </c>
-      <c r="K71" t="s">
-        <v>318</v>
+        <v>316</v>
+      </c>
+      <c r="J71" t="s">
+        <v>379</v>
       </c>
       <c r="L71" t="s">
-        <v>319</v>
+        <v>384</v>
       </c>
       <c r="M71" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N71" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O71" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P71" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q71" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R71" t="s">
-        <v>338</v>
+        <v>390</v>
       </c>
       <c r="S71" t="s">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="T71" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20">
+        <v>413</v>
+      </c>
+      <c r="U71" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B72" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D72" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E72" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F72" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G72" s="2">
         <v>45883</v>
       </c>
       <c r="H72" t="s">
-        <v>301</v>
+        <v>250</v>
       </c>
       <c r="I72" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="J72" t="s">
-        <v>316</v>
-      </c>
-      <c r="L72" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K72" t="s">
+        <v>382</v>
       </c>
       <c r="M72" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N72" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O72" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P72" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q72" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R72" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S72" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T72" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U72" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C73" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D73" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E73" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G73" s="2">
         <v>45883</v>
       </c>
       <c r="H73" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="I73" t="s">
-        <v>312</v>
-      </c>
-      <c r="K73" t="s">
-        <v>316</v>
+        <v>366</v>
+      </c>
+      <c r="J73" t="s">
+        <v>378</v>
       </c>
       <c r="L73" t="s">
-        <v>319</v>
+        <v>382</v>
       </c>
       <c r="M73" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N73" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O73" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P73" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q73" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R73" t="s">
-        <v>336</v>
+        <v>390</v>
       </c>
       <c r="S73" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="T73" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U73" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C74" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D74" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E74" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F74" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G74" s="2">
         <v>45886</v>
       </c>
       <c r="H74" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="I74" t="s">
-        <v>311</v>
+        <v>367</v>
       </c>
       <c r="J74" t="s">
-        <v>317</v>
-      </c>
-      <c r="L74" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K74" t="s">
+        <v>383</v>
       </c>
       <c r="M74" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N74" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O74" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P74" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q74" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R74" t="s">
-        <v>336</v>
+        <v>390</v>
       </c>
       <c r="S74" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="T74" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U74" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C75" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E75" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F75" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G75" s="2">
         <v>45889</v>
@@ -5826,57 +6246,60 @@
         <v>307</v>
       </c>
       <c r="I75" t="s">
-        <v>311</v>
+        <v>368</v>
       </c>
       <c r="J75" t="s">
-        <v>317</v>
-      </c>
-      <c r="L75" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K75" t="s">
+        <v>383</v>
       </c>
       <c r="M75" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N75" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O75" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P75" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q75" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R75" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="S75" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T75" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U75" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C76" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D76" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E76" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G76" s="2">
         <v>45870</v>
@@ -5885,509 +6308,536 @@
         <v>308</v>
       </c>
       <c r="I76" t="s">
-        <v>311</v>
+        <v>369</v>
       </c>
       <c r="J76" t="s">
-        <v>318</v>
-      </c>
-      <c r="L76" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K76" t="s">
+        <v>384</v>
       </c>
       <c r="M76" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N76" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O76" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P76" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q76" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R76" t="s">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="S76" t="s">
-        <v>344</v>
+        <v>405</v>
       </c>
       <c r="T76" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20">
+        <v>410</v>
+      </c>
+      <c r="U76" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C77" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D77" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E77" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G77" s="2">
         <v>45873</v>
       </c>
       <c r="H77" t="s">
-        <v>262</v>
+        <v>309</v>
       </c>
       <c r="I77" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="J77" t="s">
-        <v>316</v>
-      </c>
-      <c r="L77" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K77" t="s">
+        <v>382</v>
       </c>
       <c r="M77" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N77" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O77" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P77" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q77" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R77" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S77" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T77" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U77" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C78" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D78" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E78" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G78" s="2">
         <v>45876</v>
       </c>
       <c r="H78" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="I78" t="s">
-        <v>311</v>
+        <v>371</v>
       </c>
       <c r="J78" t="s">
-        <v>316</v>
-      </c>
-      <c r="L78" t="s">
-        <v>319</v>
+        <v>377</v>
+      </c>
+      <c r="K78" t="s">
+        <v>382</v>
       </c>
       <c r="M78" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N78" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O78" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P78" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q78" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R78" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="S78" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="T78" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20">
+        <v>412</v>
+      </c>
+      <c r="U78" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C79" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D79" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E79" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F79" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G79" s="2">
         <v>45880</v>
       </c>
       <c r="H79" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="I79" t="s">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="J79" t="s">
-        <v>317</v>
-      </c>
-      <c r="L79" t="s">
-        <v>319</v>
+        <v>379</v>
+      </c>
+      <c r="K79" t="s">
+        <v>383</v>
       </c>
       <c r="M79" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N79" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O79" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P79" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q79" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R79" t="s">
-        <v>336</v>
+        <v>390</v>
       </c>
       <c r="S79" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="T79" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U79" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B80" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E80" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F80" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G80" s="2">
         <v>45880</v>
       </c>
       <c r="H80" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="I80" t="s">
-        <v>312</v>
+        <v>372</v>
       </c>
       <c r="J80" t="s">
-        <v>317</v>
-      </c>
-      <c r="L80" t="s">
-        <v>319</v>
+        <v>378</v>
+      </c>
+      <c r="K80" t="s">
+        <v>383</v>
       </c>
       <c r="M80" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N80" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O80" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P80" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q80" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R80" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="S80" t="s">
-        <v>343</v>
+        <v>397</v>
       </c>
       <c r="T80" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20">
+        <v>409</v>
+      </c>
+      <c r="U80" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B81" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D81" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E81" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F81" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G81" s="2">
         <v>45882</v>
       </c>
       <c r="H81" t="s">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="I81" t="s">
-        <v>309</v>
+        <v>373</v>
       </c>
       <c r="J81" t="s">
-        <v>318</v>
-      </c>
-      <c r="L81" t="s">
-        <v>319</v>
+        <v>375</v>
+      </c>
+      <c r="K81" t="s">
+        <v>384</v>
       </c>
       <c r="M81" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N81" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O81" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P81" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q81" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R81" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="S81" t="s">
-        <v>344</v>
+        <v>399</v>
       </c>
       <c r="T81" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20">
+        <v>410</v>
+      </c>
+      <c r="U81" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B82" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E82" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F82" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G82" s="2">
         <v>45882</v>
       </c>
       <c r="H82" t="s">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="I82" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="J82" t="s">
-        <v>318</v>
-      </c>
-      <c r="L82" t="s">
-        <v>319</v>
+        <v>376</v>
+      </c>
+      <c r="K82" t="s">
+        <v>384</v>
       </c>
       <c r="M82" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N82" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O82" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P82" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q82" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R82" t="s">
-        <v>339</v>
+        <v>390</v>
       </c>
       <c r="S82" t="s">
-        <v>344</v>
+        <v>405</v>
       </c>
       <c r="T82" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20">
+        <v>410</v>
+      </c>
+      <c r="U82" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D83" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E83" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F83" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G83" s="2">
         <v>45885</v>
       </c>
       <c r="H83" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="I83" t="s">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="J83" t="s">
-        <v>316</v>
-      </c>
-      <c r="L83" t="s">
-        <v>319</v>
+        <v>381</v>
+      </c>
+      <c r="K83" t="s">
+        <v>382</v>
       </c>
       <c r="M83" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N83" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O83" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P83" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q83" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R83" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="S83" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="T83" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20">
+        <v>406</v>
+      </c>
+      <c r="U83" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B84" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D84" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E84" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F84" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G84" s="2">
         <v>45885</v>
       </c>
       <c r="H84" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="I84" t="s">
-        <v>314</v>
+        <v>374</v>
       </c>
       <c r="J84" t="s">
-        <v>316</v>
-      </c>
-      <c r="L84" t="s">
-        <v>319</v>
+        <v>380</v>
+      </c>
+      <c r="K84" t="s">
+        <v>382</v>
       </c>
       <c r="M84" t="s">
-        <v>320</v>
+        <v>385</v>
       </c>
       <c r="N84" t="s">
-        <v>321</v>
+        <v>386</v>
       </c>
       <c r="O84" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="P84" t="s">
-        <v>323</v>
+        <v>388</v>
       </c>
       <c r="Q84" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="R84" t="s">
-        <v>335</v>
+        <v>390</v>
       </c>
       <c r="S84" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="T84" t="s">
-        <v>348</v>
+        <v>412</v>
+      </c>
+      <c r="U84" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
   <si>
     <t>Código Produto</t>
   </si>
@@ -77,12 +77,96 @@
   </si>
   <si>
     <t>Negócio</t>
+  </si>
+  <si>
+    <t>PROD100002</t>
+  </si>
+  <si>
+    <t>PROD400001</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 100002</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400001</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PVEN - Produto Venda</t>
+  </si>
+  <si>
+    <t>100002</t>
+  </si>
+  <si>
+    <t>400001</t>
+  </si>
+  <si>
+    <t>FATURADO</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>ANDREY.ANDRADE</t>
+  </si>
+  <si>
+    <t>SAMANTA</t>
+  </si>
+  <si>
+    <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
+  </si>
+  <si>
+    <t>MATEUS BORRO MACHADO</t>
+  </si>
+  <si>
+    <t>Industrial</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>CLIENTE TESTE LTDA</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>XCD</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>Detector Fixo</t>
+  </si>
+  <si>
+    <t>Medidor de Vazão Fixo</t>
+  </si>
+  <si>
+    <t>SSO</t>
+  </si>
+  <si>
+    <t>Hidrologia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -135,11 +219,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -502,6 +587,133 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45885</v>
+      </c>
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T2" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="2">
+        <v>45870</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" t="s">
+        <v>43</v>
+      </c>
+      <c r="T3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>Código Produto</t>
   </si>
@@ -79,82 +79,34 @@
     <t>Negócio</t>
   </si>
   <si>
-    <t>PROD100002</t>
-  </si>
-  <si>
-    <t>PROD400001</t>
-  </si>
-  <si>
-    <t>Produto de Teste - Processo 100002</t>
-  </si>
-  <si>
-    <t>Produto de Teste - Processo 400001</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>PVEN - Produto Venda</t>
   </si>
   <si>
-    <t>100002</t>
-  </si>
-  <si>
-    <t>400001</t>
+    <t>TESTE2</t>
   </si>
   <si>
     <t>FATURADO</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>ANDREY.ANDRADE</t>
+    <t>30</t>
   </si>
   <si>
     <t>SAMANTA</t>
   </si>
   <si>
-    <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
-  </si>
-  <si>
     <t>MATEUS BORRO MACHADO</t>
   </si>
   <si>
-    <t>Industrial</t>
-  </si>
-  <si>
-    <t>9999</t>
-  </si>
-  <si>
-    <t>CLIENTE TESTE LTDA</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>SP</t>
+    <t>1112</t>
   </si>
   <si>
     <t>Produto</t>
   </si>
   <si>
-    <t>XCD</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>Detector Fixo</t>
-  </si>
-  <si>
-    <t>Medidor de Vazão Fixo</t>
-  </si>
-  <si>
-    <t>SSO</t>
+    <t>EXO</t>
+  </si>
+  <si>
+    <t>Sonda Serie EXO</t>
   </si>
   <si>
     <t>Hidrologia</t>
@@ -519,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -588,130 +540,47 @@
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" s="2">
+        <v>45931</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="O2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="2">
-        <v>45885</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="T2" t="s">
         <v>30</v>
       </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" t="s">
-        <v>44</v>
-      </c>
       <c r="U2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="2">
-        <v>45870</v>
-      </c>
-      <c r="H3" t="s">
         <v>31</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" t="s">
-        <v>41</v>
-      </c>
-      <c r="S3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U3" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Código Produto</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>Negócio</t>
+  </si>
+  <si>
+    <t>AAA</t>
   </si>
   <si>
     <t>PVEN - Produto Venda</t>
@@ -540,47 +543,50 @@
       </c>
     </row>
     <row r="2" spans="1:21">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="2">
         <v>45931</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -1,147 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
-  <si>
-    <t>Código Produto</t>
-  </si>
-  <si>
-    <t>Descrição Produto</t>
-  </si>
-  <si>
-    <t>Qtde Atendida</t>
-  </si>
-  <si>
-    <t>Operação</t>
-  </si>
-  <si>
-    <t>Processo</t>
-  </si>
-  <si>
-    <t>Status Processo</t>
-  </si>
-  <si>
-    <t>Data Aceite</t>
-  </si>
-  <si>
-    <t>Valor Orçado</t>
-  </si>
-  <si>
-    <t>Valor Realizado</t>
-  </si>
-  <si>
-    <t>Consultor Interno</t>
-  </si>
-  <si>
-    <t>Representante-pedido</t>
-  </si>
-  <si>
-    <t>Gerente Comercial-Pedido</t>
-  </si>
-  <si>
-    <t>Aplicação Mat./Serv.</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Nome Cliente</t>
-  </si>
-  <si>
-    <t>Cidade</t>
-  </si>
-  <si>
-    <t>UF</t>
-  </si>
-  <si>
-    <t>Tipo de Mercadoria</t>
-  </si>
-  <si>
-    <t>Subgrupo</t>
-  </si>
-  <si>
-    <t>Grupo</t>
-  </si>
-  <si>
-    <t>Negócio</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>PVEN - Produto Venda</t>
-  </si>
-  <si>
-    <t>TESTE2</t>
-  </si>
-  <si>
-    <t>FATURADO</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>DENER.MARTINS</t>
-  </si>
-  <si>
-    <t>Mateus Machado</t>
-  </si>
-  <si>
-    <t>Hidrologia</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>Produto</t>
-  </si>
-  <si>
-    <t>EXO</t>
-  </si>
-  <si>
-    <t>Sonda Serie EXO</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -156,36 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -473,126 +424,211 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código Produto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Descrição Produto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Qtde Atendida</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Operação</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Processo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status Processo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Data Aceite</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Orçado</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Realizado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Consultor Interno</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Representante-pedido</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Gerente Comercial-Pedido</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Aplicação Mat./Serv.</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Nome Cliente</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Cidade</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Mercadoria</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Subgrupo</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Negócio</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:21">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ITEM 7</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PVEN - Produto Venda</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TESTE2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FATURADO</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" t="s">
-        <v>28</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>DENER.MARTINS</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Mateus Machado</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Hidrologia</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TESTE2</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>EXO</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Sonda Serie EXO</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Hidrologia</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -1,40 +1,150 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+  <si>
+    <t>Código Produto</t>
+  </si>
+  <si>
+    <t>Descrição Produto</t>
+  </si>
+  <si>
+    <t>Qtde Atendida</t>
+  </si>
+  <si>
+    <t>Operação</t>
+  </si>
+  <si>
+    <t>Processo</t>
+  </si>
+  <si>
+    <t>Status Processo</t>
+  </si>
+  <si>
+    <t>Data Aceite</t>
+  </si>
+  <si>
+    <t>Valor Orçado</t>
+  </si>
+  <si>
+    <t>Valor Realizado</t>
+  </si>
+  <si>
+    <t>Consultor Interno</t>
+  </si>
+  <si>
+    <t>Representante-pedido</t>
+  </si>
+  <si>
+    <t>Gerente Comercial-Pedido</t>
+  </si>
+  <si>
+    <t>Aplicação Mat./Serv.</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Nome Cliente</t>
+  </si>
+  <si>
+    <t>Cidade</t>
+  </si>
+  <si>
+    <t>UF</t>
+  </si>
+  <si>
+    <t>Tipo de Mercadoria</t>
+  </si>
+  <si>
+    <t>Subgrupo</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Negócio</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>ITEM 7</t>
+  </si>
+  <si>
+    <t>PVEN - Produto Venda</t>
+  </si>
+  <si>
+    <t>TESTE2</t>
+  </si>
+  <si>
+    <t>FATURADO</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>DENER.MARTINS</t>
+  </si>
+  <si>
+    <t>Mateus Machado</t>
+  </si>
+  <si>
+    <t>Hidrologia</t>
+  </si>
+  <si>
+    <t>1112</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>EXO</t>
+  </si>
+  <si>
+    <t>Sonda Serie EXO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,94 +159,36 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -424,211 +476,129 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Código Produto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Descrição Produto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Qtde Atendida</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Operação</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Processo</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Status Processo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Data Aceite</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Orçado</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Realizado</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Consultor Interno</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Representante-pedido</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Gerente Comercial-Pedido</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Aplicação Mat./Serv.</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Nome Cliente</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Cidade</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>UF</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de Mercadoria</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Subgrupo</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Negócio</t>
-        </is>
+    <row r="1" spans="1:21">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ITEM 7</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PVEN - Produto Venda</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TESTE2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>FATURADO</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2">
         <v>45931</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>DENER.MARTINS</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Mateus Machado</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Hidrologia</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>TESTE2</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>EXO</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Sonda Serie EXO</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Hidrologia</t>
-        </is>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>